--- a/Scenarios/mom/mom_dimension_inventory.xlsx
+++ b/Scenarios/mom/mom_dimension_inventory.xlsx
@@ -53,7 +53,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'advance_cost_bands'!$A$1:$C$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'advances'!$A$1:$M$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'advances_cell_remap'!$A$1:$F$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'building_uniticon'!$A$1:$B$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'building_uniticon'!$A$1:$B$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'civ2_converted_graphics'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'concept_mask'!$A$1:$A$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'feats'!$A$1:$B$1</definedName>
@@ -61,7 +61,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'gl_text_rewrites'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'governicon_fallback'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'improveicon'!$A$1:$A$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'improvements'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'improvements'!$A$1:$F$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'players'!$A$1:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'slic_inventory'!$A$1:$G$18</definedName>
@@ -69,11 +69,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'terrain'!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'tileimp'!$A$1:$T$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'tileimp_mask'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'tileimp_mask'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'tribe_cities'!$A$1:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'unit_block_overrides'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'units'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'units'!$A$1:$P$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'wonders'!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1329,7 +1329,7 @@
         <v>63</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -10200,7 +10200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10795,20 +10795,8 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ICON_IMPROVE_AUDIENCE_HALL</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ICON_IMPROVE_AUDIENCE_HALL { FirstFrame "ICON_IMPROVE_WIZARDS_FORTRESS.tga" Movie "NULL" Gameplay "IMPROVE_AUDIENCE_HALL_GAMEPLAY" Historical "IMPROVE_AUDIENCE_HALL_HISTORICAL" Prereq "IMPROVE_AUDIENCE_HALL_PREREQ" Vari "IMPROVE_AUDIENCE_HALL_STATISTICS" Icon "ICON_IMPROVE_WIZARDS_FORTRESS.tga" LargeIcon "NULL" SmallIcon "NULL" StatText "IMPROVE_AUDIENCE_HALL_STATISTICS" }</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B50"/>
+  <autoFilter ref="A1:B49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12999,7 +12987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14514,40 +14502,8 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Audience Hall</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Mas</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>ICON_IMPROVE_WIZARDS_FORTRESS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22499,7 +22455,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ritual Tower</t>
+          <t>Processing Tower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -22555,12 +22511,12 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY</t>
+          <t>ADVANCE_ADV_URBAN_PLANNING</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -22590,12 +22546,12 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY</t>
+          <t>ADVANCE_ADV_URBAN_PLANNING</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -22625,12 +22581,12 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ADVANCE_ALCHEMY</t>
+          <t>ADVANCE_ADV_URBAN_PLANNING</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -24863,7 +24819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -25138,18 +25094,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>TILEIMP_PROCESSING_TOWER</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>out_of_genre</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TILEIMP_UNDERSEA_TUNNEL</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>out_of_genre</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26108,12 +26077,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -26121,11 +26090,12 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="29" customWidth="1" min="14" max="14"/>
-    <col width="31" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="29" customWidth="1" min="15" max="15"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26136,70 +26106,75 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>art_cell_index</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>move</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>defense</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>firepower</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>prereq</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>sprite</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>sound_select1</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>sound_move</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>sound_attack</t>
         </is>
@@ -26213,70 +26188,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Peasants</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>0a</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>ICON_UNIT_PEASANTS</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>SPRITE_PEASANTS</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_PEASANTS</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>SOUND_MOVE_PEASANTS</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_PEASANTS</t>
         </is>
@@ -26290,70 +26270,75 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Zombies</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Rfg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ICON_UNIT_ZOMBIES</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>SPRITE_ZOMBIES</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_ZOMBIES</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>SOUND_MOVE_ZOMBIES</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_ZOMBIES</t>
         </is>
@@ -26367,70 +26352,75 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Spearmen</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>ICON_UNIT_SPEARMEN</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>SPRITE_SPEARMEN</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_SPEARMEN</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>SOUND_MOVE_SPEARMEN</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_SPEARMEN</t>
         </is>
@@ -26444,70 +26434,75 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Swordsmen</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bro</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>ICON_UNIT_SWORDSMEN</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>SPRITE_SWORDSMEN</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_SWORDSMEN</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>SOUND_MOVE_SWORDSMEN</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_SWORDSMEN</t>
         </is>
@@ -26521,70 +26516,75 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Phantom Warriors</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>The</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>ICON_UNIT_PHANTOM_WARRIORS</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>SPRITE_PHANTOM_WARRIORS</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_PHANTOM_WARRIORS</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>SOUND_MOVE_PHANTOM_WARRIORS</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_PHANTOM_WARRIORS</t>
         </is>
@@ -26598,70 +26598,75 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Hell Hounds</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>ICON_UNIT_HELL_HOUNDS</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>SPRITE_HELL_HOUNDS</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_HELL_HOUNDS</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>SOUND_MOVE_HELL_HOUNDS</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_HELL_HOUNDS</t>
         </is>
@@ -26675,70 +26680,75 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Warbears</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Plu</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>ICON_UNIT_WARBEARS</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>SPRITE_WARBEARS</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WARBEARS</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WARBEARS</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WARBEARS</t>
         </is>
@@ -26752,70 +26762,75 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Warlock</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>12a</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>AFl</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>ICON_UNIT_WARLOCK</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>SPRITE_WARLOCK</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WARLOCK</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WARLOCK</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WARLOCK</t>
         </is>
@@ -26829,70 +26844,75 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Ariel</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>8d</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>ICON_UNIT_ARIEL</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>SPRITE_ARIEL</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_ARIEL</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>SOUND_MOVE_ARIEL</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_ARIEL</t>
         </is>
@@ -26906,70 +26926,75 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Jafar</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>ICON_UNIT_JAFAR</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>SPRITE_JAFAR</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_JAFAR</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>SOUND_MOVE_JAFAR</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_JAFAR</t>
         </is>
@@ -26983,70 +27008,75 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Rjak</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>ICON_UNIT_RJAK</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>SPRITE_RJAK</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_RJAK</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>SOUND_MOVE_RJAK</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_RJAK</t>
         </is>
@@ -27060,70 +27090,75 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Tauron</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>3f</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>ICON_UNIT_TAURON</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>SPRITE_TAURON</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_TAURON</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>SOUND_MOVE_TAURON</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_TAURON</t>
         </is>
@@ -27137,70 +27172,75 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Serena</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>ICON_UNIT_SERENA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>SPRITE_SERENA</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_SERENA</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>SOUND_MOVE_SERENA</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_SERENA</t>
         </is>
@@ -27214,70 +27254,75 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Freya</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>ICON_UNIT_FREYA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>SPRITE_FREYA</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_FREYA</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>SOUND_MOVE_FREYA</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_FREYA</t>
         </is>
@@ -27291,70 +27336,75 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Alorra</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>ICON_UNIT_ALORRA</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>SPRITE_ALORRA</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_ALORRA</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>SOUND_MOVE_ALORRA</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_ALORRA</t>
         </is>
@@ -27368,70 +27418,75 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Centaurs</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Env</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>ICON_UNIT_CENTAURS</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>SPRITE_CENTAURS</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_CENTAURS</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>SOUND_MOVE_CENTAURS</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_CENTAURS</t>
         </is>
@@ -27445,70 +27500,75 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Elven Archers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Cor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>ICON_UNIT_ELVEN_ARCHERS</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>SPRITE_ELVEN_ARCHERS</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_ELVEN_ARCHERS</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>SOUND_MOVE_ELVEN_ARCHERS</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_ELVEN_ARCHERS</t>
         </is>
@@ -27522,70 +27582,75 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Mage</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>X6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>ICON_UNIT_MAGE</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>SPRITE_MAGE</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_MAGE</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>SOUND_MOVE_MAGE</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_MAGE</t>
         </is>
@@ -27599,70 +27664,75 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Wyvern</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Che</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>ICON_UNIT_WYVERN</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>SPRITE_WYVERN</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WYVERN</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WYVERN</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WYVERN</t>
         </is>
@@ -27676,70 +27746,75 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Knights</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Chi</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>ICON_UNIT_KNIGHTS</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>SPRITE_KNIGHTS</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_KNIGHTS</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>SOUND_MOVE_KNIGHTS</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_KNIGHTS</t>
         </is>
@@ -27753,70 +27828,75 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Paladins</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Ldr</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>ICON_UNIT_PALADINS</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>SPRITE_PALADINS</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_PALADINS</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>SOUND_MOVE_PALADINS</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_PALADINS</t>
         </is>
@@ -27830,70 +27910,75 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Unicorn</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>3a</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Lab</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>ICON_UNIT_UNICORN</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>SPRITE_UNICORN</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_UNICORN</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>SOUND_MOVE_UNICORN</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_UNICORN</t>
         </is>
@@ -27907,70 +27992,75 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Iron Golem</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Esp</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>ICON_UNIT_IRON_GOLEM</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>SPRITE_IRON_GOLEM</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_IRON_GOLEM</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>SOUND_MOVE_IRON_GOLEM</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_IRON_GOLEM</t>
         </is>
@@ -27984,70 +28074,75 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Catapult</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Mat</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>ICON_UNIT_CATAPULT</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>SPRITE_CATAPULT</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_CATAPULT</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>SOUND_MOVE_CATAPULT</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_CATAPULT</t>
         </is>
@@ -28061,70 +28156,75 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Steam Cannon</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>10a</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>X3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>ICON_UNIT_STEAM_CANNON</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>SPRITE_STEAM_CANNON</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_STEAM_CANNON</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>SOUND_MOVE_STEAM_CANNON</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_STEAM_CANNON</t>
         </is>
@@ -28138,70 +28238,75 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>B6</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>ICON_UNIT_B6</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>SPRITE_B6</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B6</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B6</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B6</t>
         </is>
@@ -28215,70 +28320,75 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>ICON_UNIT_B3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>SPRITE_B3</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B3</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B3</t>
         </is>
@@ -28292,70 +28402,75 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>ICON_UNIT_B9</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>SPRITE_B9</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B9</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B9</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B9</t>
         </is>
@@ -28369,70 +28484,75 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Efreet</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Met</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>ICON_UNIT_EFREET</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>SPRITE_EFREET</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_EFREET</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>SOUND_MOVE_EFREET</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_EFREET</t>
         </is>
@@ -28446,70 +28566,75 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>Wraith</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Rob</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>ICON_UNIT_WRAITH</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>SPRITE_WRAITH</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WRAITH</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WRAITH</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WRAITH</t>
         </is>
@@ -28523,70 +28648,75 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Griffin</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>X4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>ICON_UNIT_GRIFFIN</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>SPRITE_GRIFFIN</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_GRIFFIN</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>SOUND_MOVE_GRIFFIN</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_GRIFFIN</t>
         </is>
@@ -28600,70 +28730,75 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>Pegasus</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Las</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>ICON_UNIT_PEGASUS</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>SPRITE_PEGASUS</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_PEGASUS</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>SOUND_MOVE_PEGASUS</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_PEGASUS</t>
         </is>
@@ -28677,70 +28812,75 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Galley</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>ICON_UNIT_GALLEY</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>SPRITE_GALLEY</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_GALLEY</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>SOUND_MOVE_GALLEY</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_GALLEY</t>
         </is>
@@ -28754,70 +28894,75 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>Warship</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Eng</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>ICON_UNIT_WARSHIP</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>SPRITE_WARSHIP</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WARSHIP</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WARSHIP</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WARSHIP</t>
         </is>
@@ -28831,70 +28976,75 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Hydra</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>12a</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>3h</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Mob</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>ICON_UNIT_HYDRA</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>SPRITE_HYDRA</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_HYDRA</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>SOUND_MOVE_HYDRA</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_HYDRA</t>
         </is>
@@ -28908,70 +29058,75 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Airship</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>X3</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>ICON_UNIT_AIRSHIP</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>SPRITE_AIRSHIP</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_AIRSHIP</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>SOUND_MOVE_AIRSHIP</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_AIRSHIP</t>
         </is>
@@ -28985,70 +29140,75 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Minotaur</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>War</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>ICON_UNIT_MINOTAUR</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>SPRITE_MINOTAUR</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_MINOTAUR</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>SOUND_MOVE_MINOTAUR</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_MINOTAUR</t>
         </is>
@@ -29062,70 +29222,75 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>War Troll</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>7a</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>3h</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Tac</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>ICON_UNIT_WAR_TROLL</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>SPRITE_WAR_TROLL</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WAR_TROLL</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WAR_TROLL</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WAR_TROLL</t>
         </is>
@@ -29139,70 +29304,75 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>Gargoyle</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>ICON_UNIT_GARGOYLE</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>SPRITE_GARGOYLE</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_GARGOYLE</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>SOUND_MOVE_GARGOYLE</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_GARGOYLE</t>
         </is>
@@ -29216,70 +29386,75 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>Guardian Spirit</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>3h</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Inv</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>ICON_UNIT_GUARDIAN_SPIRIT</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>SPRITE_GUARDIAN_SPIRIT</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_GUARDIAN_SPIRIT</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>SOUND_MOVE_GUARDIAN_SPIRIT</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_GUARDIAN_SPIRIT</t>
         </is>
@@ -29293,70 +29468,75 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Cockatrice</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>3f</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>ICON_UNIT_COCKATRICE</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>SPRITE_COCKATRICE</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_COCKATRICE</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>SOUND_MOVE_COCKATRICE</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_COCKATRICE</t>
         </is>
@@ -29370,70 +29550,75 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>B7</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>ICON_UNIT_B7</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>SPRITE_B7</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B7</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B7</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B7</t>
         </is>
@@ -29447,70 +29632,75 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>B8</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>ICON_UNIT_B8</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>SPRITE_B8</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B8</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B8</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B8</t>
         </is>
@@ -29524,70 +29714,75 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>ICON_UNIT_B3</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>SPRITE_B3</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B3</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B3</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B3</t>
         </is>
@@ -29601,70 +29796,75 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>Salamander</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>10a</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>X5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>ICON_UNIT_SALAMANDER</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>SPRITE_SALAMANDER</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_SALAMANDER</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>SOUND_MOVE_SALAMANDER</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_SALAMANDER</t>
         </is>
@@ -29678,70 +29878,75 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>Infernal Device</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>99a</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>NF</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>ICON_UNIT_INFERNAL_DEVICE</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>SPRITE_INFERNAL_DEVICE</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_INFERNAL_DEVICE</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>SOUND_MOVE_INFERNAL_DEVICE</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_INFERNAL_DEVICE</t>
         </is>
@@ -29755,70 +29960,75 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Minion</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>0a</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>0d</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Wri</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>ICON_UNIT_MINION</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>SPRITE_MINION</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_MINION</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>SOUND_MOVE_MINION</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_MINION</t>
         </is>
@@ -29832,70 +30042,75 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>Demon</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>SFl</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>ICON_UNIT_DEMON</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>SPRITE_DEMON</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_DEMON</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>SOUND_MOVE_DEMON</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_DEMON</t>
         </is>
@@ -29909,70 +30124,75 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Caravan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>0a</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Tra</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>ICON_UNIT_CARAVAN</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>SPRITE_CARAVAN</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_CARAVAN</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>SOUND_MOVE_CARAVAN</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_CARAVAN</t>
         </is>
@@ -29986,70 +30206,75 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>B5</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>ICON_UNIT_B5</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>SPRITE_B5</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B5</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B5</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B5</t>
         </is>
@@ -30063,70 +30288,75 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>ICON_UNIT_B4</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>SPRITE_B4</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_B4</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>SOUND_MOVE_B4</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_B4</t>
         </is>
@@ -30140,70 +30370,75 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>War Mammoth</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>10a</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>5d</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>3h</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Exp</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>ICON_UNIT_WAR_MAMMOTH</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>SPRITE_WAR_MAMMOTH</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WAR_MAMMOTH</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WAR_MAMMOTH</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WAR_MAMMOTH</t>
         </is>
@@ -30217,70 +30452,75 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Storm Giant</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>NP</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>ICON_UNIT_STORM_GIANT</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>SPRITE_STORM_GIANT</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_STORM_GIANT</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>SOUND_MOVE_STORM_GIANT</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_STORM_GIANT</t>
         </is>
@@ -30294,70 +30534,75 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>Air Elemental</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>X2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>ICON_UNIT_AIR_ELEMENTAL</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>SPRITE_AIR_ELEMENTAL</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_AIR_ELEMENTAL</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>SOUND_MOVE_AIR_ELEMENTAL</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_AIR_ELEMENTAL</t>
         </is>
@@ -30371,70 +30616,75 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>Storm Drake</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>12a</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>3h</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Pla</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>ICON_UNIT_STORM_DRAKE</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>SPRITE_STORM_DRAKE</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_STORM_DRAKE</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>SOUND_MOVE_STORM_DRAKE</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_STORM_DRAKE</t>
         </is>
@@ -30448,70 +30698,75 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>Warrax</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>ICON_UNIT_WARRAX</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>SPRITE_WARRAX</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_WARRAX</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>SOUND_MOVE_WARRAX</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_WARRAX</t>
         </is>
@@ -30525,70 +30780,75 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
           <t>Undead Dragon</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>12a</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>6d</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>ICON_UNIT_UNDEAD_DRAGON</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>SPRITE_UNDEAD_DRAGON</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_UNDEAD_DRAGON</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>SOUND_MOVE_UNDEAD_DRAGON</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_UNDEAD_DRAGON</t>
         </is>
@@ -30602,70 +30862,75 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>Great Wyrm</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>15a</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>9d</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>6h</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>ICON_UNIT_GREAT_WYRM</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>SPRITE_GREAT_WYRM</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_GREAT_WYRM</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>SOUND_MOVE_GREAT_WYRM</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_GREAT_WYRM</t>
         </is>
@@ -30679,70 +30944,75 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>Behemoth</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>5a</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>4d</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Rad</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>ICON_UNIT_BEHEMOTH</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>SPRITE_BEHEMOTH</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_BEHEMOTH</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>SOUND_MOVE_BEHEMOTH</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_BEHEMOTH</t>
         </is>
@@ -30756,70 +31026,75 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>Malleus</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>8a</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Mys</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>ICON_UNIT_MALLEUS</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>SPRITE_MALLEUS</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_MALLEUS</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>SOUND_MOVE_MALLEUS</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_MALLEUS</t>
         </is>
@@ -30833,70 +31108,75 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>Merfolk</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>4a</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>3d</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>U3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>ICON_UNIT_MERFOLK</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>SPRITE_MERFOLK</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_MERFOLK</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>SOUND_MOVE_MERFOLK</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_MERFOLK</t>
         </is>
@@ -30910,70 +31190,75 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Archangel</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>12a</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>12d</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>2f</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Mag</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>ICON_UNIT_ARCHANGEL</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>SPRITE_ARCHANGEL</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_ARCHANGEL</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>SOUND_MOVE_ARCHANGEL</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_ARCHANGEL</t>
         </is>
@@ -30987,77 +31272,82 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>Settler</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>0a</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2d</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>2h</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1f</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>nil</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>ICON_UNIT_SETTLER</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>SPRITE_SETTLER</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>SOUND_SELECT1_SETTLER</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>SOUND_MOVE_SETTLER</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>SOUND_ATTACK_SETTLER</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O64"/>
+  <autoFilter ref="A1:P64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Scenarios/mom/mom_dimension_inventory.xlsx
+++ b/Scenarios/mom/mom_dimension_inventory.xlsx
@@ -40,6 +40,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_mask" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="units" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="wonders" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="slic_index" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'index'!$A$10:$E$43</definedName>
@@ -64,7 +66,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'improvements'!$A$1:$F$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'order_mask'!$A$1:$A$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'players'!$A$1:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'slic_inventory'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'slic_inventory'!$A$1:$G$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'sprite_pick_rules'!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'stub_advances'!$A$1:$D$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'terrain'!$A$1:$J$27</definedName>
@@ -75,6 +77,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'unit_mask'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'units'!$A$1:$P$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'wonders'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'slic'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'slic_index'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,7 +107,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +117,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDDDDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,12 +137,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1119,7 +1132,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E33" t="n">
         <v>7</v>
@@ -1463,7 +1476,6 @@
           <t>Alchemy</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Cmp</t>
@@ -1526,7 +1538,6 @@
           <t>Alphabet</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>nil</t>
@@ -1589,7 +1600,6 @@
           <t>Animism</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Uni</t>
@@ -1652,7 +1662,6 @@
           <t>Astrology</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Mys</t>
@@ -1715,7 +1724,6 @@
           <t>Eldritch Lore</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Ast</t>
@@ -1778,7 +1786,6 @@
           <t>User Def Tech A</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>no</t>
@@ -1841,7 +1848,6 @@
           <t>Banking</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Rep</t>
@@ -1904,7 +1910,6 @@
           <t>Bridge Building</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Iro</t>
@@ -1967,7 +1972,6 @@
           <t>Bronze Working</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>nil</t>
@@ -2030,7 +2034,6 @@
           <t>Ceremonial Burial</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>nil</t>
@@ -2093,7 +2096,6 @@
           <t>Greater Fauna Lore</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>X4</t>
@@ -2156,7 +2158,6 @@
           <t>Chivalry</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Feu</t>
@@ -2219,7 +2220,6 @@
           <t>Code of Laws</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Alp</t>
@@ -2282,7 +2282,6 @@
           <t>Healing</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Ast</t>
@@ -2345,7 +2344,6 @@
           <t>Lesser Enchanments</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>no</t>
@@ -2408,7 +2406,6 @@
           <t>Extra Advance 4</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>no</t>
@@ -2471,7 +2468,6 @@
           <t>Metamorphosis</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>E1</t>
@@ -2534,7 +2530,6 @@
           <t>Construction</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Mas</t>
@@ -2597,7 +2592,6 @@
           <t>Pantheism</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Cer</t>
@@ -2660,7 +2654,6 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Bro</t>
@@ -2723,7 +2716,6 @@
           <t>Rune Lore</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>X6</t>
@@ -2786,7 +2778,6 @@
           <t>Sea Mastery</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>Iro</t>
@@ -2849,7 +2840,6 @@
           <t>Shamanism</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>nil</t>
@@ -2912,7 +2902,6 @@
           <t>Thaumaturgy</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>The</t>
@@ -2975,7 +2964,6 @@
           <t>Tactics</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Tac</t>
@@ -3038,7 +3026,6 @@
           <t>Feudalism</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>War</t>
@@ -3101,7 +3088,6 @@
           <t>Wizardry</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>AFl</t>
@@ -3164,7 +3150,6 @@
           <t>Glyphs</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>no</t>
@@ -3227,7 +3212,6 @@
           <t>Life Magic</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3290,7 +3274,6 @@
           <t>Chaos Magic</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3353,7 +3336,6 @@
           <t>Sorcery</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>NF</t>
@@ -3416,7 +3398,6 @@
           <t>Life Lore</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Gen</t>
@@ -3479,7 +3460,6 @@
           <t>Iron Working</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>Bro</t>
@@ -3542,7 +3522,6 @@
           <t>Life Adept</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Inv</t>
@@ -3605,7 +3584,6 @@
           <t>Life Mage</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Lab</t>
@@ -3668,7 +3646,6 @@
           <t>Holy Warriors</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>Chi</t>
@@ -3731,7 +3708,6 @@
           <t>Literacy</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Wri</t>
@@ -3794,7 +3770,6 @@
           <t>Life Wizard</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Las</t>
@@ -3857,7 +3832,6 @@
           <t>Life Master</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Too</t>
@@ -3920,7 +3894,6 @@
           <t>Map Making</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>Alp</t>
@@ -3983,7 +3956,6 @@
           <t>Masonry</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>nil</t>
@@ -4046,7 +4018,6 @@
           <t>Chaos Lore</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>Gun</t>
@@ -4109,7 +4080,6 @@
           <t>Mathematics</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Alp</t>
@@ -4172,7 +4142,6 @@
           <t>Chaos Adept</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>MP</t>
@@ -4235,7 +4204,6 @@
           <t>Chaos Mage</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Med</t>
@@ -4298,7 +4266,6 @@
           <t>Chaos Wizard</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>Met</t>
@@ -4361,7 +4328,6 @@
           <t>Chaos Master</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Min</t>
@@ -4424,7 +4390,6 @@
           <t>Monarchy</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Cer</t>
@@ -4487,7 +4452,6 @@
           <t>Theology</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Phi</t>
@@ -4550,7 +4514,6 @@
           <t>Mysticism</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Cer</t>
@@ -4613,7 +4576,6 @@
           <t>Navigation</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Sea</t>
@@ -4676,7 +4638,6 @@
           <t>Grand Mastery</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>Exp</t>
@@ -4739,7 +4700,6 @@
           <t>Sorcery Mage</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>X2</t>
@@ -4802,7 +4762,6 @@
           <t>Philosophy</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>Mys</t>
@@ -4865,7 +4824,6 @@
           <t>Sorcery Wizard</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>NP</t>
@@ -4928,7 +4886,6 @@
           <t>Sorcery Master</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Phy</t>
@@ -4991,7 +4948,6 @@
           <t>Nature Lore</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>X1</t>
@@ -5054,7 +5010,6 @@
           <t>Nature Adept</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>Plu</t>
@@ -5117,7 +5072,6 @@
           <t>Pottery</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>nil</t>
@@ -5180,7 +5134,6 @@
           <t>Nature Mage</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>PT</t>
@@ -5243,7 +5196,6 @@
           <t>Greater Enchantments</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>no</t>
@@ -5306,7 +5258,6 @@
           <t>Nature Wizard</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Rad</t>
@@ -5369,7 +5320,6 @@
           <t>Nature Master</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Rec</t>
@@ -5432,7 +5382,6 @@
           <t>Death Lore</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>U2</t>
@@ -5495,7 +5444,6 @@
           <t>The Republic</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Lit</t>
@@ -5558,7 +5506,6 @@
           <t>Death Adept</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Rfg</t>
@@ -5621,7 +5568,6 @@
           <t>Sanitation</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>CA</t>
@@ -5684,7 +5630,6 @@
           <t>Seafaring</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Map</t>
@@ -5747,7 +5692,6 @@
           <t>Death Mage</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Rob</t>
@@ -5810,7 +5754,6 @@
           <t>Death Wizard</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>SFl</t>
@@ -5873,7 +5816,6 @@
           <t>Death Master</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>Sth</t>
@@ -5936,7 +5878,6 @@
           <t>Leadership</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>Chi</t>
@@ -5999,7 +5940,6 @@
           <t>Sorcerous Lore</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Hor</t>
@@ -6062,7 +6002,6 @@
           <t>Trade</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>Cur</t>
@@ -6125,7 +6064,6 @@
           <t>University</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>Mat</t>
@@ -6188,7 +6126,6 @@
           <t>Warrior Code</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>nil</t>
@@ -6251,7 +6188,6 @@
           <t>Writing</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Alp</t>
@@ -6314,7 +6250,6 @@
           <t>Future Technology</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>Sth</t>
@@ -6377,7 +6312,6 @@
           <t>Forces of Nature</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>Amp</t>
@@ -6440,7 +6374,6 @@
           <t>Death Magic</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>NF</t>
@@ -6503,7 +6436,6 @@
           <t>Sea Lore</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>Nav</t>
@@ -6566,7 +6498,6 @@
           <t>Nature Magic</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>NF</t>
@@ -6629,7 +6560,6 @@
           <t>Sorcery Adept</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>The</t>
@@ -6692,7 +6622,6 @@
           <t>Artificing</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>Esp</t>
@@ -6755,7 +6684,6 @@
           <t>Lesser Fauna Lore</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>Amp</t>
@@ -6818,7 +6746,6 @@
           <t>Pyrotechnics</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>Ato</t>
@@ -6881,7 +6808,6 @@
           <t>Occult Studies</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>Env</t>
@@ -10909,8 +10835,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11049,8 +10973,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11078,8 +11000,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11107,8 +11027,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11136,8 +11054,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11165,8 +11081,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11194,8 +11108,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11223,8 +11135,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11252,8 +11162,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11281,8 +11189,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11310,8 +11216,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11339,8 +11243,6 @@
           <t>UNITS.BMP</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -11368,14 +11270,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11393,14 +11292,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11418,14 +11314,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11443,14 +11336,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11468,14 +11358,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11493,14 +11380,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11518,14 +11402,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11543,14 +11424,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11568,14 +11446,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11593,14 +11468,11 @@
           <t>ICONS.BMP</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G27"/>
@@ -11744,7 +11616,6 @@
           <t>set</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Requires:
@@ -11768,7 +11639,6 @@
           <t>set</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
@@ -11791,7 +11661,6 @@
           <t>set</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Requires:
@@ -11843,8 +11712,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11862,8 +11729,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11881,8 +11746,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11900,8 +11763,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11925,7 +11786,6 @@
 &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11949,7 +11809,6 @@
 Magnetic Levitation Trains, or &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_MAGLEV&gt;Maglevs&lt;e&gt;, are transit systems that whiz along the surface of the earth at speeds well in excess of any other form of land transportation.  As a &lt;L:DATABASE_CONCEPTS,CONCEPT_TILE_IMPROVEMENTS&gt;Tile Improvement&lt;e&gt;, they are the fastest way to get around, dramatically reducing the movement costs associated with any terrain they are built on.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11967,7 +11826,6 @@
           <t>set</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Requires:
@@ -11991,7 +11849,6 @@
           <t>set</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Enchanted Roads reduce the movement cost for units.  They are an improvement on &lt;L:DATABASE_TILE_IMPROVEMENTS,TILEIMP_ROAD&gt;Roads&lt;e&gt;, and allow units to travel greater distances in a single turn.  Build them on any land tile.</t>
@@ -12041,8 +11898,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12060,8 +11915,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12079,8 +11932,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12098,8 +11949,6 @@
           <t>pop</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E18"/>
@@ -12222,7 +12071,6 @@
           <t>Undersea Tunnels enable land units to travel across water.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12254,7 +12102,6 @@
           <t>Shopping Malls</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12262,7 +12109,6 @@
           <t>Shopping Mall</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B13"/>
@@ -14737,7 +14583,6 @@
           <t>Ariel</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -14877,7 +14722,6 @@
           <t>Jafar</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -14945,7 +14789,6 @@
           <t>Rjak</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -15013,7 +14856,6 @@
           <t>Tauron</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>mom_tribe</t>
@@ -15121,8 +14963,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15185,8 +15025,6 @@
           <t>PERSONALITY_GHANDI</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15249,8 +15087,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15313,8 +15149,6 @@
           <t>PERSONALITY_KAHN</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15377,8 +15211,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15441,8 +15273,6 @@
           <t>PERSONALITY_CEASAR</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15505,8 +15335,6 @@
           <t>PERSONALITY_GHANDI</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15569,8 +15397,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15633,8 +15459,6 @@
           <t>PERSONALITY_KAHN</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15697,8 +15521,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15761,8 +15583,6 @@
           <t>PERSONALITY_MEDICI</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15825,8 +15645,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15889,8 +15707,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -15953,8 +15769,6 @@
           <t>PERSONALITY_NADER</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -16017,8 +15831,6 @@
           <t>PERSONALITY_TELLER</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -16081,8 +15893,6 @@
           <t>PERSONALITY_GHANDI</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Sioux -&gt; NATIVE_AMERICAN</t>
@@ -16105,7 +15915,6 @@
           <t>Saladin</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>historical</t>
@@ -16141,8 +15950,6 @@
           <t>PERSONALITY_NADER</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -16165,7 +15972,6 @@
           <t>Atawallpa</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>historical</t>
@@ -16201,8 +16007,6 @@
           <t>PERSONALITY_CEASAR</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Direct match</t>
@@ -16221,13 +16025,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -16273,7 +16077,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scenario.slc</t>
+          <t>mom_city_effects.slc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -16283,22 +16087,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MomSlicAlive</t>
+          <t>MomSphereAdvanceBlessings</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>HandleEvent(GrantAdvance) post</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>one-shot liveness probe; DisableTrigger self</t>
+          <t>sphere magic-advance milestone: grant blessing building + spawn sphere unit (Chaos = random gold)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -16310,32 +16114,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tutorial.slc</t>
+          <t>mom_city_effects.slc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MomSphereCityEffects</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HandleEvent(CreateBuilding) post</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>retires stock tut2_main.slc tutorial triggers</t>
+          <t>+30 burst gold on themed building completion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -16362,7 +16166,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -16399,7 +16203,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_2)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -16436,7 +16240,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_3)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -16473,7 +16277,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_4)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -16510,7 +16314,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_5)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -16547,7 +16351,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_6)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -16584,7 +16388,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_7)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16621,7 +16425,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>int_f(int_t p)</t>
+          <t>int_f(int_t p_8)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16653,17 +16457,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MomGrantSphereBuilding</t>
+          <t>MomGrantLifeBuilding</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>void_f(int_t p; int_t buildingType)</t>
+          <t>void_f(int_t p_9)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>grant a themed building in the player's first city if absent</t>
+          <t>grant the Life-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -16690,17 +16494,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MomSpawnSphereUnit</t>
+          <t>MomGrantNatureBuilding</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>void_f(int_t p; int_t unitType)</t>
+          <t>void_f(int_t p_10)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CreateUnit in first city (integer player index)</t>
+          <t>grant the Nature-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -16717,27 +16521,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mom_turns.slc</t>
+          <t>mom_func.slc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MomSphereTurnBlessings</t>
+          <t>MomGrantSorceryBuilding</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HandleEvent(BeginTurn) post</t>
+          <t>void_f(int_t p_11)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>per-turn sphere gold income by faction</t>
+          <t>grant the Sorcery-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -16754,27 +16558,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mom_city_effects.slc</t>
+          <t>mom_func.slc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MomSphereAdvanceBlessings</t>
+          <t>MomGrantDeathBuilding</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>void_f(int_t p_12)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>sphere magic-advance milestone: grant blessing building + spawn sphere unit (Chaos = random gold)</t>
+          <t>grant the Death-sphere themed building in the player's first city</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -16791,27 +16595,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mom_city_effects.slc</t>
+          <t>mom_func.slc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MomSphereCityEffects</t>
+          <t>MomSpawnSphereUnit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HandleEvent(CreateBuilding) post</t>
+          <t>void_f(int_t p_13, int_t unitType)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+30 burst gold on themed building completion</t>
+          <t>CreateUnit in first city (integer player index)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -16828,32 +16632,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mom_msg.slc</t>
+          <t>mom_magic.slc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>handler</t>
+          <t>function</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MomSphereBlessingMessages</t>
+          <t>MomRecalcMagicPerTurn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HandleEvent(GrantAdvance) post</t>
+          <t>int_f(int_t mp_1)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -16870,37 +16674,1257 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>handler</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>MomMagicPoolTick</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>per-turn mana accrual into MomMagicCur, capped at the 100 pool ceiling</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mom_magic.slc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MomMagicSchoolGrant</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MomSphereBlessingMessages</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MomSummonOrderTick</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MomMsgSlicAlive</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>segment: SLIC liveness confirmation text</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MomBlessLife</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>segment: Life sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MomBlessNature</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>segment: Nature sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MomBlessSorcery</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>segment: Sorcery sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MomBlessDeath</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>segment: Death sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MomBlessChaos</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>segment: Chaos sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MomSummonGuard</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MomSummonBear</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>segment: Nature summon result (War Bear)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MomSummonMage</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>segment: Sorcery summon result (Mage)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MomSummonZombie</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>segment: Death summon result (Zombies)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MomSummonHound</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>segment: Chaos summon result (Hell Hound)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MomSummonNoMana</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MomMagicPower</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>segment: mana pool / income readout body</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MagicMenu</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MomCastFlameStrike</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Chaos spell: damage the nearest enemy unit; targeting scan inlined to stay inside the Class 1 call budget</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MomCastDemonStrike</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same reason</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MomSpellShowBook</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MomSpellMenuTick</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>per-turn tick that resolves a queued spellbook selection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MomOpenSpellbook</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>UI trigger bound to the control-panel MagicButton</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MomSpellAICast</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>let AI players cast their sphere's spell when mana allows</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MomMsgSpellbook</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>segment: generic spellbook menu</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MomMsgSpellbookChaos</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>segment: Chaos-specific spellbook menu</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MomMsgDemonCast</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>segment: Demon Strike cast confirmation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MomMsgFlameCast</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>segment: Flame Strike cast confirmation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MomMsgNoTarget</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>segment: no enemy unit in range</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MomMsgNoMana</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MomMsgNotChaos</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>segment: caster's sphere does not grant this spell</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mom_turns.slc</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MomSphereTurnBlessings</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>per-turn sphere gold income by faction</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>scenario.slc</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MoM magic system (power pool / school multipliers / spells / mana nodes / AI) per specs/slic-magic-system.md — built on base-verified SLIC</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
+      <c r="E50">
+        <f>============================================================================</f>
+        <v/>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tutorial.slc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>retires stock tut2_main.slc tutorial triggers</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16970,7 +17994,6 @@
           <t>attack_ge</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>35</t>
@@ -16998,8 +18021,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>SPRITE_FIRE_TRIREME</t>
@@ -17027,7 +18048,6 @@
           <t>device</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>SPRITE_CRUISE_MISSILE</t>
@@ -17050,8 +18070,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>SPRITE_FIGHTER</t>
@@ -17064,7 +18082,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>name</t>
@@ -17075,7 +18092,6 @@
           <t>archer|bow|elven</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>SPRITE_LONGBOWMAN</t>
@@ -17088,7 +18104,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>name</t>
@@ -17099,7 +18114,6 @@
           <t>cannon|steam</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>SPRITE_CANNON</t>
@@ -17112,7 +18126,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>name</t>
@@ -17123,7 +18136,6 @@
           <t>catapult</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>SPRITE_CANNON</t>
@@ -17136,7 +18148,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>name</t>
@@ -17147,7 +18158,6 @@
           <t>mammoth</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>SPRITE_ELEPHANT_WARRIOR</t>
@@ -17160,7 +18170,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>name</t>
@@ -17171,7 +18180,6 @@
           <t>cavalry|unicorn|paladin|horseman</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>SPRITE_CAVALRY</t>
@@ -17184,7 +18192,6 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>name</t>
@@ -17195,7 +18202,6 @@
           <t>peasant|settler</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>SPRITE_SETTLER</t>
@@ -17208,13 +18214,11 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>attack_ge</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>40</t>
@@ -17232,13 +18236,11 @@
           <t>sprite</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>attack_ge</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>20</t>
@@ -17256,7 +18258,6 @@
           <t>size</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>name</t>
@@ -17267,7 +18268,6 @@
           <t>giant|wyrm|dragon|behemoth|mammoth</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Large</t>
@@ -17280,13 +18280,11 @@
           <t>size</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>hp_ge</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>3</t>
@@ -17304,14 +18302,11 @@
           <t>size</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Small</t>
@@ -18566,7 +19561,6 @@
           <t>ADVANCE_ADVANCED_COMPOSITES</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18916,8 +19910,6 @@
           <t>Air; Sea; ShallowWater</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_FOUR; TERRAIN_WATER_SHALLOW_GOOD_THREE</t>
@@ -18960,8 +19952,6 @@
           <t>Air; Sea</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
@@ -19004,8 +19994,6 @@
           <t>Air; Sea</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>TERRAIN_ARCTIC_MOUNTAIN_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_TWO; TERRAIN_WHITE_HILL_GOOD_ONE; TERRAIN_ARCTIC_MOUNTAIN_GOOD_FOUR</t>
@@ -19048,8 +20036,6 @@
           <t>Air; Sea; ShallowWater</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_BEACH_GOOD_ONE; TERRAIN_WATER_BEACH_GOOD_TWO; TERRAIN_WATER_BEACH_GOOD_THREE</t>
@@ -19092,8 +20078,6 @@
           <t>Air; Sea</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
@@ -19136,8 +20120,6 @@
           <t>Air; Sea</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
@@ -19180,8 +20162,6 @@
           <t>Air; Sea</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP_GOOD_TWO; TERRAIN_WATER_DEEP_GOOD_ONE; TERRAIN_WATER_DEEP_GOOD_THREE</t>
@@ -19224,13 +20204,11 @@
           <t>Air; Land</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>ADVANCE_CONSERVATION</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19476,8 +20454,6 @@
           <t>Air; Sea; ShallowWater</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
@@ -19520,8 +20496,6 @@
           <t>Air; Sea; ShallowWater</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_SHALLOW_GOOD_ONE; TERRAIN_WATER_SHALLOW_GOOD_TWO; TERRAIN_WATER_SHALLOW_GOOD_THREE; TERRAIN_WATER_SHALLOW_GOOD_FOUR</t>
@@ -19564,9 +20538,6 @@
           <t>Air; Land</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19604,9 +20575,6 @@
           <t>Air; Land</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J27"/>
@@ -19809,7 +20777,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>500</t>
@@ -19887,7 +20854,6 @@
           <t>TERRAIN_DESERT TERRAIN_GRASSLAND TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>10</t>
@@ -19920,14 +20886,11 @@
           <t>TILEIMP_ADVANCED_MINES</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>5</t>
@@ -19960,14 +20923,11 @@
           <t>TILEIMP_ADVANCED_MINES</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>30</t>
@@ -20055,7 +21015,6 @@
           <t>TERRAIN_WATER_DEEP</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>30</t>
@@ -20088,14 +21047,11 @@
           <t>TILEIMP_ADVANCED_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_RIFT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>45</t>
@@ -20128,14 +21084,11 @@
           <t>TILEIMP_ADVANCED_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>60</t>
@@ -20265,8 +21218,6 @@
           <t>TILEIMP_AIR_BASES</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
@@ -20401,8 +21352,6 @@
           <t>TILEIMP_AUTOMATED_FISHERIES</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP TERRAIN_WATER_RIFT TERRAIN_WATER_TRENCH</t>
@@ -20440,8 +21389,6 @@
           <t>TILEIMP_AUTOMATED_FISHERIES</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_VOLCANO</t>
@@ -20534,7 +21481,6 @@
           <t>TERRAIN_WATER_DEEP</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>ADVANCE_OIL_REFINING</t>
@@ -20562,14 +21508,11 @@
           <t>TILEIMP_DRILLING_PLATFORM</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_KELP TERRAIN_WATER_REEF</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>ADVANCE_OIL_REFINING</t>
@@ -20597,14 +21540,11 @@
           <t>TILEIMP_DRILLING_PLATFORM</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_RIFT TERRAIN_WATER_SHALLOW TERRAIN_WATER_SHELF</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>ADVANCE_OIL_REFINING</t>
@@ -20632,14 +21572,11 @@
           <t>TILEIMP_DRILLING_PLATFORM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_TRENCH TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>ADVANCE_OIL_REFINING</t>
@@ -20841,8 +21778,6 @@
           <t>TILEIMP_FISHERIES</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP TERRAIN_WATER_RIFT TERRAIN_WATER_TRENCH</t>
@@ -20880,8 +21815,6 @@
           <t>TILEIMP_FISHERIES</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_VOLCANO</t>
@@ -21297,8 +22230,6 @@
           <t>TILEIMP_MAGLEV</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_FOREST TERRAIN_HILL TERRAIN_JUNGLE TERRAIN_WHITE_HILL</t>
@@ -21341,8 +22272,6 @@
           <t>TILEIMP_MAGLEV</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>TERRAIN_SWAMP TERRAIN_TUNDRA</t>
@@ -21385,8 +22314,6 @@
           <t>TILEIMP_MAGLEV</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
@@ -21521,8 +22448,6 @@
           <t>TILEIMP_MEGA_MINES</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
@@ -21565,8 +22490,6 @@
           <t>TILEIMP_MEGA_MINES</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
@@ -21664,7 +22587,6 @@
           <t>TERRAIN_WATER_DEEP</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -21692,14 +22614,11 @@
           <t>TILEIMP_MEGA_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_RIFT TERRAIN_WATER_SHALLOW TERRAIN_WATER_SHELF</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -21727,14 +22646,11 @@
           <t>TILEIMP_MEGA_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_TRENCH TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -21817,7 +22733,6 @@
           <t>TERRAIN_DESERT TERRAIN_GRASSLAND TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>5</t>
@@ -21845,14 +22760,11 @@
           <t>TILEIMP_MINES</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>10</t>
@@ -21880,14 +22792,11 @@
           <t>TILEIMP_MINES</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>15</t>
@@ -22104,8 +23013,6 @@
           <t>TILEIMP_NETS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP TERRAIN_WATER_RIFT TERRAIN_WATER_TRENCH</t>
@@ -22143,8 +23050,6 @@
           <t>TILEIMP_NETS</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_VOLCANO</t>
@@ -22237,7 +23142,6 @@
           <t>TERRAIN_DESERT TERRAIN_GRASSLAND TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22265,14 +23169,11 @@
           <t>TILEIMP_OUTLET_MALL</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22300,14 +23201,11 @@
           <t>TILEIMP_OUTLET_MALL</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22390,7 +23288,6 @@
           <t>TERRAIN_WATER_BEACH TERRAIN_WATER_KELP TERRAIN_WATER_REEF TERRAIN_WATER_SHALLOW TERRAIN_WATER_SHELF</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>ADVANCE_SEAFARING</t>
@@ -22418,14 +23315,11 @@
           <t>TILEIMP_PORT</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_RIFT TERRAIN_WATER_TRENCH TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>ADVANCE_SEAFARING</t>
@@ -22508,7 +23402,6 @@
           <t>TERRAIN_DESERT TERRAIN_GRASSLAND TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22536,14 +23429,11 @@
           <t>TILEIMP_PROCESSING_TOWER</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22571,14 +23461,11 @@
           <t>TILEIMP_PROCESSING_TOWER</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>ADVANCE_ADV_URBAN_PLANNING</t>
@@ -22800,8 +23687,6 @@
           <t>TILEIMP_RAILROAD</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_FOREST TERRAIN_HILL TERRAIN_JUNGLE TERRAIN_WHITE_HILL</t>
@@ -22844,8 +23729,6 @@
           <t>TILEIMP_RAILROAD</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>TERRAIN_SWAMP TERRAIN_TUNDRA</t>
@@ -22888,8 +23771,6 @@
           <t>TILEIMP_RAILROAD</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
@@ -23024,8 +23905,6 @@
           <t>TILEIMP_ROAD</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_FOREST TERRAIN_HILL TERRAIN_JUNGLE TERRAIN_WHITE_HILL</t>
@@ -23068,8 +23947,6 @@
           <t>TILEIMP_ROAD</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>TERRAIN_SWAMP TERRAIN_TUNDRA</t>
@@ -23112,8 +23989,6 @@
           <t>TILEIMP_ROAD</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
@@ -23243,8 +24118,6 @@
           <t>TILEIMP_SONAR_BUOYS</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_DEEP TERRAIN_WATER_RIFT TERRAIN_WATER_TRENCH</t>
@@ -23282,8 +24155,6 @@
           <t>TILEIMP_SONAR_BUOYS</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_VOLCANO</t>
@@ -23331,7 +24202,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_BROWN_HILL</t>
@@ -23372,7 +24242,6 @@
           <t>TERRAIN_BROWN_HILL</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23410,7 +24279,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_BROWN_MOUNTAIN</t>
@@ -23451,7 +24319,6 @@
           <t>TERRAIN_BROWN_MOUNTAIN</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23489,7 +24356,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_DESERT</t>
@@ -23530,7 +24396,6 @@
           <t>TERRAIN_DESERT</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23568,7 +24433,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_FOREST</t>
@@ -23609,7 +24473,6 @@
           <t>TERRAIN_FOREST</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23647,7 +24510,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_GRASSLAND</t>
@@ -23688,7 +24550,6 @@
           <t>TERRAIN_GRASSLAND</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23726,7 +24587,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_HILL</t>
@@ -23767,7 +24627,6 @@
           <t>TERRAIN_HILL</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23805,7 +24664,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_JUNGLE</t>
@@ -23846,7 +24704,6 @@
           <t>TERRAIN_JUNGLE</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23884,7 +24741,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_MOUNTAIN</t>
@@ -23925,7 +24781,6 @@
           <t>TERRAIN_MOUNTAIN</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -23963,7 +24818,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_PLAINS</t>
@@ -24004,7 +24858,6 @@
           <t>TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -24042,7 +24895,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_SWAMP</t>
@@ -24083,7 +24935,6 @@
           <t>TERRAIN_SWAMP</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -24121,7 +24972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_WHITE_HILL</t>
@@ -24162,7 +25012,6 @@
           <t>TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -24200,7 +25049,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>ICON_TILEIMP_TERRAFORM_WHITE_MOUNTAIN</t>
@@ -24241,7 +25089,6 @@
           <t>TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>ADVANCE_TERRAFORMING</t>
@@ -24324,7 +25171,6 @@
           <t>TERRAIN_DESERT TERRAIN_GRASSLAND TERRAIN_PLAINS</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>ADVANCE_TRADE</t>
@@ -24352,14 +25198,11 @@
           <t>TILEIMP_TRADING_POST</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_HILL TERRAIN_HILL TERRAIN_WHITE_HILL</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>ADVANCE_TRADE</t>
@@ -24387,14 +25230,11 @@
           <t>TILEIMP_TRADING_POST</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>TERRAIN_BROWN_MOUNTAIN TERRAIN_MOUNTAIN TERRAIN_WHITE_MOUNTAIN</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>ADVANCE_TRADE</t>
@@ -24477,7 +25317,6 @@
           <t>TERRAIN_WATER_DEEP</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -24505,14 +25344,11 @@
           <t>TILEIMP_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_RIFT TERRAIN_WATER_SHALLOW TERRAIN_WATER_SHELF</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -24540,14 +25376,11 @@
           <t>TILEIMP_UNDERSEA_MINES</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_TRENCH TERRAIN_WATER_VOLCANO</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>ADVANCE_ULTRAPRESSURE_MACHINERY</t>
@@ -24667,8 +25500,6 @@
           <t>TILEIMP_UNDERSEA_TUNNEL</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>TERRAIN_WATER_TRENCH TERRAIN_WATER_VOLCANO</t>
@@ -25076,7 +25907,6 @@
           <t>out_of_genre</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25089,7 +25919,6 @@
           <t>out_of_genre</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25102,7 +25931,6 @@
           <t>out_of_genre</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25115,7 +25943,6 @@
           <t>out_of_genre</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C18"/>
@@ -32151,6 +32978,4373 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>include_order</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>constants</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>handlers</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>triggers</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>segments</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>n_decls</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>bytes</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>scenario.slc</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <f>============================================================================</f>
+        <v/>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>3613</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>//=============================================================================
+// scenario.slc - Master of Magic scenario SLIC entry point (Phase A baseline)
+//=============================================================================
+// Loaded because base ctp2_data/default/gamedata/script.slc does
+//   #include "scenario.slc"
+// and this scenario-level file shadows the (intentionally empty) base stub.
+//
+// INCLUDE ORDER CONTRACT (later phases):
+//   1. mom_func.slc         helpers/predicates ONLY (no handlers)
+//   2. mom_turns.slc        BeginTurn sphere income
+//   3. mom_city_effects.slc GrantAdvance / CreateBuilding milestone rewards
+//   4. mom_msg.slc          messagebox blocks LAST
+//
+// RULES (see lessons_learned.md [SLIC] and specs/slic-sphere-layer.md):
+//   - PURE ASCII ONLY in .slc files (the SLIC lexer chokes on multi-byte).
+//   - Faction check: NUMERIC player index (p == 1 = Life). TRIBES_* are civ-DB
+//     record names, NOT SLIC symbols -- SLIC cannot resolve them.
+//   - playerTurn is EVENT-LOCAL: helpers take int_t p as an argument.
+//   - No hardcoded player[0]/unit[0]/city[0] as a civ assumption.
+//   - Every UNIT_/IMPROVE_/ADVANCE_/WONDER_ symbol must exist in the DBs
+//     (engine silently auto-creates unknowns). Run validate_all_surfaces.py.
+//=============================================================================
+// Phase A liveness probe: REMOVED 2026-07-25.
+//
+// It showed a one-time proof-of-life Message on the human's first BeginTurn to
+// prove the scenario SLIC layer parsed. That question is long since settled by
+// stronger evidence -- 25/25 clean headless turns, the 'j' MagicMenu alertbox,
+// working summons, and interactive alertbox buttons whose state survives a turn
+// boundary. The probe was scaffolding that outlived its job.
+//
+// It had to go rather than merely be ignored: a CTP2 Message window is an aui
+// surface, and aui polls GetCursorPos, so a PostMessage click can never dismiss
+// one (measured -- every candidate send factor left closed=False, while the same
+// clicks fell through onto the map behind it and scrolled the view into
+// unexplored black). So this box sat pinned over the top-left of EVERY frame for
+// the rest of the game, occluding the map region the unit-visibility check
+// measures, and each dismissal attempt panned the map. One removed debug line
+// closes both.
+//
+// Player-facing magic status lives on the 'j' MagicMenu alertbox, which IS
+// dismissable by both a human and the harness.
+// Phase B1 sphere-magic modules. Include order (func before turns): mom_func.slc
+// defines the helpers that mom_turns.slc's BeginTurn handler calls. B1a wires the
+// Life sphere only; B1b fans out to the other spheres, and B2/Phase C add
+// mom_city_effects.slc and mom_msg.slc (last) per the entry-point contract.
+#include "mom_func.slc"
+#include "mom_turns.slc"
+#include "mom_city_effects.slc"
+#include "mom_msg.slc"
+#include "mom_magic.slc"
+// B2 spellbook. Wired 2026-07-25 -- the file was complete but never included, so
+// its MagicButton trigger (already referenced at controlpanel.ldl:774) had no
+// handler behind it. Included LAST: it reads the MomMagic* file-scope globals
+// declared in mom_func.slc, so declaration-before-use requires func to load first.
+// Pre-checked static name collisions across all six modules: 24 segments, 0 dups
+// (segment/segment duplication is the documented load-AV class). Every other
+// repeated identifier (p, i, j, summon, focusCount) is indented, i.e. declared
+// inside a handler body and therefore segment-local, not file scope.
+#include "mom_spells.slc"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>MoM sphere helpers -- all five spheres (Phase B1b, fanned out from the proven</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>int_t MomMagicCur[31];       // current magic power per player
+int_t MomMagicMax[31];       // max storage per player (a school sets this in M2)
+int_t MomMagicPerTurn[31];   // last computed per-turn generation
+int_t MomMagicCurDisp;       // plain display scalars for the popup: {scalar} is base-verified
+int_t MomMagicMaxDisp;       // (AlexanderTheGreat {cityScore}); array-indexed {Arr[Idx]} is
+int_t MomMagicGenDisp;       // unsupported and silently drops the whole message
+int_t MomSpellPromptArmed[31];   // re-arm below threshold, fire once on crossing
+int_t MomSpellCurDisp;           // display scalars for the spellbook popup
+int_t MomSpellMaxDisp;
+int_t MomSummonChoice[31];
+int_t MomMagicShownTurn[31]; // per-round re-entry latch for the popup (flood safety)
+int_t MomMagicSchoolPct[31]; // per-turn multiplier as integer percent (M2); 0 read as 100</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>int_f MomPlayerIsLife(int_t p_1)
+{
+    // Player 1 == Tribes of Life (civ #1). Numeric index, not TRIBES_LIFE (undefined in SLIC).
+    if (p_1 == 1) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsNature(int_t p_2)
+{
+    if (p_2 == 2) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsSorcery(int_t p_3)
+{
+    if (p_3 == 3) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsDeath(int_t p_4)
+{
+    if (p_4 == 4) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsChaos(int_t p_5)
+{
+    if (p_5 == 5) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomCountLifeBlessings(int_t p_6)
+{
+    int_t i;
+    int_t blessingCount;
+    city_t tmpCity;
+    blessingCount = 0;
+    // player[0] is the event player. NEVER player[1] -- see MomSpawnSphereUnit.
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) {
+                blessingCount = blessingCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_CITY_WALLS")) {
+                blessingCount = blessingCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) {
+                blessingCount = blessingCount + 1;
+            }
+        }
+    }
+    return blessingCount;
+}
+int_f MomCountNatureFoci(int_t p_7)
+{
+    int_t i;
+    int_t focusCount;
+    city_t tmpCity;
+    // NOTE: the original design also counted Gaia's Shrine, but the fugly fix made it a
+    // WONDER (removed from buildings.txt), so it is no longer a city improvement. Dropped
+    // here to keep only verified improvement refs; it could be re-added later via a
+    // CityHasWonder/WonderDB check if that focus is wanted.
+    focusCount = 0;
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_GRANARY")) {
+                focusCount = focusCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) {
+                focusCount = focusCount + 2;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) {
+                focusCount = focusCount + 1;
+            }
+        }
+    }
+    return focusCount;
+}
+int_f MomCountSorceryFoci(int_t p_8)
+{
+    int_t i;
+    int_t focusCount;
+    city_t tmpCity;
+    focusCount = 0;
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) {
+                focusCount = focusCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) {
+                focusCount = focusCount + 2;
+            }
+        }
+    }
+    return focusCount;
+}
+void_f MomGrantLifeBuilding(int_t p_9)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_TEMPLE));
+        }
+    }
+}
+void_f MomGrantNatureBuilding(int_t p_10)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_GRANARY")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_GRANARY));
+        }
+    }
+}
+void_f MomGrantSorceryBuilding(int_t p_11)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_LIBRARY));
+        }
+    }
+}
+void_f MomGrantDeathBuilding(int_t p_12)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_BARRACKS));
+        }
+    }
+}
+void_f MomSpawnSphereUnit(int_t p_13, int_t unitType)
+{
+    city_t tmpCity;
+    location_t spawnLoc;
+    location_t tryLoc;
+    int_t d;
+    int_t placed;
+    // NEVER player[1]: player[] is the event ARG array (size 1), so player[1] is
+    // out of bounds -- the same rule mom_turns.slc documents. It did not raise a
+    // SLIC error here because the write silently no-ops and the .cities read then
+    // returns 0, so this function quietly spawned NOTHING on every call. Every
+    // caller passes the handler's own player, which IS player[0].
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            // ADJACENT PLACEMENT, 2026-07-25. This used to spawn on tmpCity.location
+            // unconditionally, so every summon piled onto the capital tile. CTP2 draws
+            // exactly ONE unit per tile, and CellUnitList::GetTopVisibleUnitOfMoveType
+            // orders own units by MaxMovePoints -- GUARDIAN_SPIRIT is 200, SPEARMEN is
+            // 100, so a single summon permanently hid every unit the player built there
+            // ("you can't find the unit on the map despite us building one"). Placing
+            // the summon on a free land neighbour leaves the garrison's draw slot alone.
+            //
+            // Builtins only, no nested user-function call: this runs from the
+            // BeginTurn handler body and the 2-level chain is the known 0xC0000005.
+            // WORLD_DIRECTION 0..7 are the eight neighbours (directions.h); GetNeighbor
+            // returns 0 at a map edge, where its out-arg is not written -- so the
+            // return value must gate the read.
+            spawnLoc = tmpCity.location;
+            placed = 0;
+            for (d = 0; d &lt; 8; d = d + 1) {
+                if (placed == 0) {
+                    if (GetNeighbor(tmpCity.location, d, tryLoc)) {
+                        if (!IsWater(tryLoc)) {
+                            if (GetUnitsAtLocation(tryLoc) == 0) {
+                                spawnLoc = tryLoc;
+                                placed = 1;
+                            }
+                        }
+                    }
+                }
+            }
+            CreateUnit(p_13, unitType, spawnLoc, 1);
+        }
+    }
+}</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>9881</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>// MoM sphere helpers -- all five spheres (Phase B1b, fanned out from the proven
+// Life element in B1a).
+//
+// SLIC API (base-verified against ctp2.map builtins + reference scenarios):
+//   - faction check: NUMERIC player index. TRIBES_* are civilisation-DB record names,
+//     NOT SLIC symbols -- SLIC cannot resolve them ("Symbol TRIBES_LIFE is undefined").
+//     Seating convention: player N = civ N (Life 1, Nature 2, Sorcery 3, Death 4,
+//     Chaos 5), matching the reference-scenario idiom `player[0] == 1`.
+//   - iterate a player's cities: GetCityByIndex(player[p], i, tmpCity) guarded by
+//     CityIsValid(tmpCity).
+//   - membership: CityHasBuilding(city, "IMPROVE_X") -- the engine REQUIRES a hard
+//     quoted string literal (slicfunc.cpp: SA_TYPE_HARD_STRING, looked up via StringDB).
+//     BuildingDB() refs or variables raise "Wrong type of argument".
+//   Helpers take int_t p (a player index); callers pass the event-local player[0].
+int_f MomPlayerIsLife(int_t p_1)
+{
+    // Player 1 == Tribes of Life (civ #1). Numeric index, not TRIBES_LIFE (undefined in SLIC).
+    if (p_1 == 1) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsNature(int_t p_2)
+{
+    if (p_2 == 2) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsSorcery(int_t p_3)
+{
+    if (p_3 == 3) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsDeath(int_t p_4)
+{
+    if (p_4 == 4) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomPlayerIsChaos(int_t p_5)
+{
+    if (p_5 == 5) {
+        return 1;
+    }
+    return 0;
+}
+int_f MomCountLifeBlessings(int_t p_6)
+{
+    int_t i;
+    int_t blessingCount;
+    city_t tmpCity;
+    blessingCount = 0;
+    // player[0] is the event player. NEVER player[1] -- see MomSpawnSphereUnit.
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) {
+                blessingCount = blessingCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_CITY_WALLS")) {
+                blessingCount = blessingCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_WIZARDS_FORTRESS")) {
+                blessingCount = blessingCount + 1;
+            }
+        }
+    }
+    return blessingCount;
+}
+int_f MomCountNatureFoci(int_t p_7)
+{
+    int_t i;
+    int_t focusCount;
+    city_t tmpCity;
+    // NOTE: the original design also counted Gaia's Shrine, but the fugly fix made it a
+    // WONDER (removed from buildings.txt), so it is no longer a city improvement. Dropped
+    // here to keep only verified improvement refs; it could be re-added later via a
+    // CityHasWonder/WonderDB check if that focus is wanted.
+    focusCount = 0;
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_GRANARY")) {
+                focusCount = focusCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_PRIMAL_SOURCE")) {
+                focusCount = focusCount + 2;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_FANTASTIC_STABLE")) {
+                focusCount = focusCount + 1;
+            }
+        }
+    }
+    return focusCount;
+}
+int_f MomCountSorceryFoci(int_t p_8)
+{
+    int_t i;
+    int_t focusCount;
+    city_t tmpCity;
+    focusCount = 0;
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            if (CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) {
+                focusCount = focusCount + 1;
+            }
+            if (CityHasBuilding(tmpCity, "IMPROVE_BEACON_OF_WISDOM")) {
+                focusCount = focusCount + 2;
+            }
+        }
+    }
+    return focusCount;
+}
+// --- Milestone-event helpers (Phase B2) ---
+// Grant a one-time blessing building in the player's first city (if absent), and spawn
+// a sphere unit there. CreateUnit/CreateBuilding take base-verified forms: CreateUnit's
+// first arg is the INTEGER player index (NOT player[p]); membership uses BuildingDB().
+// NOTE: CityHasBuilding requires a HARD STRING LITERAL (variable args return
+// SFN_ERROR at runtime), so the grant helper is fanned out per sphere instead of
+// being generic over a BuildingDB() variable. CreateBuilding itself is fine with
+// a variable (engine takes an int), but we still guard to avoid re-running
+// AddImprovement side effects (capitol designation / border regeneration).
+void_f MomGrantLifeBuilding(int_t p_9)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_TEMPLE")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_TEMPLE));
+        }
+    }
+}
+void_f MomGrantNatureBuilding(int_t p_10)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_GRANARY")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_GRANARY));
+        }
+    }
+}
+void_f MomGrantSorceryBuilding(int_t p_11)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_LIBRARY")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_LIBRARY));
+        }
+    }
+}
+void_f MomGrantDeathBuilding(int_t p_12)
+{
+    city_t tmpCity;
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity) &amp;&amp; !CityHasBuilding(tmpCity, "IMPROVE_BARRACKS")) {
+            CreateBuilding(tmpCity, BuildingDB(IMPROVE_BARRACKS));
+        }
+    }
+}
+void_f MomSpawnSphereUnit(int_t p_13, int_t unitType)
+{
+    city_t tmpCity;
+    location_t spawnLoc;
+    location_t tryLoc;
+    int_t d;
+    int_t placed;
+    // NEVER player[1]: player[] is the event ARG array (size 1), so player[1] is
+    // out of bounds -- the same rule mom_turns.slc documents. It did not raise a
+    // SLIC error here because the write silently no-ops and the .cities read then
+    // returns 0, so this function quietly spawned NOTHING on every call. Every
+    // caller passes the handler's own player, which IS player[0].
+    if (player[0].cities) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            // ADJACENT PLACEMENT, 2026-07-25. This used to spawn on tmpCity.location
+            // unconditionally, so every summon piled onto the capital tile. CTP2 draws
+            // exactly ONE unit per tile, and CellUnitList::GetTopVisibleUnitOfMoveType
+            // orders own units by MaxMovePoints -- GUARDIAN_SPIRIT is 200, SPEARMEN is
+            // 100, so a single summon permanently hid every unit the player built there
+            // ("you can't find the unit on the map despite us building one"). Placing
+            // the summon on a free land neighbour leaves the garrison's draw slot alone.
+            //
+            // Builtins only, no nested user-function call: this runs from the
+            // BeginTurn handler body and the 2-level chain is the known 0xC0000005.
+            // WORLD_DIRECTION 0..7 are the eight neighbours (directions.h); GetNeighbor
+            // returns 0 at a map edge, where its out-arg is not written -- so the
+            // return value must gate the read.
+            spawnLoc = tmpCity.location;
+            placed = 0;
+            for (d = 0; d &lt; 8; d = d + 1) {
+                if (placed == 0) {
+                    if (GetNeighbor(tmpCity.location, d, tryLoc)) {
+                        if (!IsWater(tryLoc)) {
+                            if (GetUnitsAtLocation(tryLoc) == 0) {
+                                spawnLoc = tryLoc;
+                                placed = 1;
+                            }
+                        }
+                    }
+                }
+            }
+            CreateUnit(p_13, unitType, spawnLoc, 1);
+        }
+    }
+}
+// Magic power state (used by mom_magic.slc, declared here because mom_func.slc
+// loads first -- keeps declaration-before-use across the include order).
+int_t MomMagicCur[31];       // current magic power per player
+int_t MomMagicMax[31];       // max storage per player (a school sets this in M2)
+int_t MomMagicPerTurn[31];   // last computed per-turn generation
+int_t MomMagicCurDisp;       // plain display scalars for the popup: {scalar} is base-verified
+int_t MomMagicMaxDisp;       // (AlexanderTheGreat {cityScore}); array-indexed {Arr[Idx]} is
+int_t MomMagicGenDisp;       // unsupported and silently drops the whole message
+// Phase D spellbook globals (mom_spells.slc). They live HERE, not there, for the
+// same reason MomMagic*Disp does: mom_func.slc is the FIRST include, and a
+// messagebox/alertbox segment that interpolates a global declared in a
+// later-loading file is the documented MagicMenu failure mode.
+int_t MomSpellPromptArmed[31];   // re-arm below threshold, fire once on crossing
+int_t MomSpellCurDisp;           // display scalars for the spellbook popup
+int_t MomSpellMaxDisp;
+// INTERACTIVITY LINK 7 (the last open link): does a button-body mutation SURVIVE
+// a turn boundary and get CONSUMED by a handler that changes ENGINE state?
+// Links 3-6 (click reaches the button, body executes, mutates, mutation is
+// readable on reopen) were closed 2026-07-24; all of that happened inside one
+// turn, so none of it speaks to persistence across BeginTurn.
+// 0 = no pending order. Set by an alertbox arm, consumed and cleared by
+// MomSummonOrderTick in mom_msg.slc.
+int_t MomSummonChoice[31];
+int_t MomMagicShownTurn[31]; // per-round re-entry latch for the popup (flood safety)
+int_t MomMagicSchoolPct[31]; // per-turn multiplier as integer percent (M2); 0 read as 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>mom_turns.slc</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>MoM sphere per-turn income -- all five spheres (Phase B1b, fanned out from the</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) 'MomSphereTurnBlessings' post {
+    int_t p;
+    int_t turnGold;
+    // player[0] is the BeginTurn event's single player arg (the turn player).
+    // p captures its INTEGER index for AddGold()/MomPlayerIsX(); the turn
+    // player's own data is read via player[0].cities/.units. NEVER player[p]:
+    // player[N] indexes the event ARG array (size 1 here), so player[1+] throws
+    // "Array index 1 out of bounds" (SlicArray::Lookup).
+    p = player[0];
+    turnGold = 0;
+    if (MomPlayerIsLife(p)) {
+        turnGold = 6 + player[0].cities * 3 + MomCountLifeBlessings(p) * 4;
+    } elseif (MomPlayerIsNature(p)) {
+        turnGold = 4 + player[0].cities * 2 + MomCountNatureFoci(p) * 3;
+    } elseif (MomPlayerIsSorcery(p)) {
+        turnGold = 4 + player[0].cities * 2 + MomCountSorceryFoci(p) * 3;
+    } elseif (MomPlayerIsDeath(p)) {
+        turnGold = 4 + player[0].cities * 2 + (player[0].units / 3);
+    } elseif (MomPlayerIsChaos(p)) {
+        turnGold = 4 + Random(6 + player[0].cities * 10);
+    }
+    if (turnGold &gt; 0) {
+        AddGold(p, turnGold);
+    }
+}</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1718</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>// MoM sphere per-turn income -- all five spheres (Phase B1b, fanned out from the
+// proven Life element in B1a).
+//
+// The BeginTurn event-local player is player[0] (NOT `playerTurn`, which is an
+// undefined symbol). player[0] used in an integer context yields the turn player's
+// index (reference scenarios do `if(player[0] == 1)`); AddGold takes that integer
+// index, NOT a player[] object. No latch is needed: this is intended once-per-
+// player-per-turn income (unlike Message, AddGold does not flood the event queue).
+// Each player only takes its own sphere's branch, so every faction (human + AI) is paid.
+HandleEvent(BeginTurn) 'MomSphereTurnBlessings' post {
+    int_t p;
+    int_t turnGold;
+    // player[0] is the BeginTurn event's single player arg (the turn player).
+    // p captures its INTEGER index for AddGold()/MomPlayerIsX(); the turn
+    // player's own data is read via player[0].cities/.units. NEVER player[p]:
+    // player[N] indexes the event ARG array (size 1 here), so player[1+] throws
+    // "Array index 1 out of bounds" (SlicArray::Lookup).
+    p = player[0];
+    turnGold = 0;
+    if (MomPlayerIsLife(p)) {
+        turnGold = 6 + player[0].cities * 3 + MomCountLifeBlessings(p) * 4;
+    } elseif (MomPlayerIsNature(p)) {
+        turnGold = 4 + player[0].cities * 2 + MomCountNatureFoci(p) * 3;
+    } elseif (MomPlayerIsSorcery(p)) {
+        turnGold = 4 + player[0].cities * 2 + MomCountSorceryFoci(p) * 3;
+    } elseif (MomPlayerIsDeath(p)) {
+        turnGold = 4 + player[0].cities * 2 + (player[0].units / 3);
+    } elseif (MomPlayerIsChaos(p)) {
+        turnGold = 4 + Random(6 + player[0].cities * 10);
+    }
+    if (turnGold &gt; 0) {
+        AddGold(p, turnGold);
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>mom_city_effects.slc</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>MoM sphere milestone events -- all five spheres (Phase B2b, fanned out from the</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) 'MomSphereAdvanceBlessings' post {
+    int_t p;
+    p = player[0];
+    // See mom_magic.slc 'MomMagicSchoolGrant': advance[] is NOT populated by
+    // GrantAdvance, and assigning value[0] into it does not make it readable
+    // (MEASURED 2026-07-25 -- this line errored here too). value[0] IS the
+    // granted advance index; compare it to AdvanceDB() directly.
+    if (value[0] != 0) {
+        if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+            MomGrantLifeBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT));
+        } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+            MomGrantNatureBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS));
+        } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+            MomGrantSorceryBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE));
+        } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+            MomGrantDeathBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES));
+        } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+            AddGold(p, 50 + Random(100));
+        }
+    }
+}
+HandleEvent(CreateBuilding) 'MomSphereCityEffects' post {
+    int_t p;
+    int_t burstGold;
+    p = city[0].owner;
+    burstGold = 0;
+    // Same class as the GrantAdvance handlers above: CreateBuilding does not
+    // populate building[], and assigning value[0] into it does not make it
+    // readable. value[0] IS the improvement index -- compare it directly.
+    if (MomPlayerIsLife(p)) {
+        if (value[0] == BuildingDB(IMPROVE_TEMPLE)
+        || value[0] == BuildingDB(IMPROVE_CITY_WALLS)
+        || value[0] == BuildingDB(IMPROVE_WIZARDS_FORTRESS)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsNature(p)) {
+        if (value[0] == BuildingDB(IMPROVE_GRANARY)
+        || value[0] == BuildingDB(IMPROVE_PRIMAL_SOURCE)
+        || value[0] == BuildingDB(IMPROVE_FANTASTIC_STABLE)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsSorcery(p)) {
+        if (value[0] == BuildingDB(IMPROVE_LIBRARY)
+        || value[0] == BuildingDB(IMPROVE_BEACON_OF_WISDOM)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsDeath(p)) {
+        if (value[0] == BuildingDB(IMPROVE_BARRACKS)
+        || value[0] == BuildingDB(IMPROVE_MECHANICIANS_GUILD)) {
+            burstGold = 30;
+        }
+    }
+    if (burstGold &gt; 0) {
+        AddGold(p, burstGold);
+    }
+}</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4110</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>// MoM sphere milestone events -- all five spheres (Phase B2b, fanned out from the
+// proven Life element in B2a). Kept separate from the turn loop; #included after
+// mom_turns.slc.
+//
+// Event-local API (base-verified, stock tut2_main.slc):
+//   GrantAdvance : player = player[0]; granted advance = value[0]
+//                  (advance[0] = value[0]; value[0] == AdvanceDB(...)).
+//   CreateBuilding: city = city[0]; built improvement = value[0]; player = city[0].owner
+//                  (building[0] = value[0]; value[0] == BuildingDB(...)).
+//   AddGold takes the INTEGER player index. No latch needed: GrantAdvance fires once per
+//   advance per player; the CreateBuilding burst is a per-completion AddGold (no flood).
+//
+// Per-sphere mapping (derived from the mom_turns.slc B1 themes + DB-verified symbols;
+// CLERIC/SOLAR_HARNESS/ACADEMY from the old spec checklist do NOT exist and are omitted):
+//   Sphere   Advance        Blessing (building + unit)            Burst buildings (+30 each)
+//   Life     LIFE_MAGIC     TEMPLE   + GUARDIAN_SPIRIT            TEMPLE, CITY_WALLS, WIZARDS_FORTRESS
+//   Nature   NATURE_MAGIC   GRANARY  + WARBEARS                   GRANARY, PRIMAL_SOURCE, FANTASTIC_STABLE
+//   Sorcery  SORCERY        LIBRARY  + MAGE                       LIBRARY, BEACON_OF_WISDOM
+//   Death    DEATH_MAGIC    BARRACKS + ZOMBIES                    BARRACKS, MECHANICIANS_GUILD
+//   Chaos    CHAOS_MAGIC    random gold windfall (no bldg/unit)   -- (matches its B1 random-gold theme)
+HandleEvent(GrantAdvance) 'MomSphereAdvanceBlessings' post {
+    int_t p;
+    p = player[0];
+    // See mom_magic.slc 'MomMagicSchoolGrant': advance[] is NOT populated by
+    // GrantAdvance, and assigning value[0] into it does not make it readable
+    // (MEASURED 2026-07-25 -- this line errored here too). value[0] IS the
+    // granted advance index; compare it to AdvanceDB() directly.
+    if (value[0] != 0) {
+        if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+            MomGrantLifeBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT));
+        } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+            MomGrantNatureBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_WARBEARS));
+        } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+            MomGrantSorceryBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_MAGE));
+        } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+            MomGrantDeathBuilding(p);
+            MomSpawnSphereUnit(p, UnitDB(UNIT_ZOMBIES));
+        } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+            AddGold(p, 50 + Random(100));
+        }
+    }
+}
+HandleEvent(CreateBuilding) 'MomSphereCityEffects' post {
+    int_t p;
+    int_t burstGold;
+    p = city[0].owner;
+    burstGold = 0;
+    // Same class as the GrantAdvance handlers above: CreateBuilding does not
+    // populate building[], and assigning value[0] into it does not make it
+    // readable. value[0] IS the improvement index -- compare it directly.
+    if (MomPlayerIsLife(p)) {
+        if (value[0] == BuildingDB(IMPROVE_TEMPLE)
+        || value[0] == BuildingDB(IMPROVE_CITY_WALLS)
+        || value[0] == BuildingDB(IMPROVE_WIZARDS_FORTRESS)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsNature(p)) {
+        if (value[0] == BuildingDB(IMPROVE_GRANARY)
+        || value[0] == BuildingDB(IMPROVE_PRIMAL_SOURCE)
+        || value[0] == BuildingDB(IMPROVE_FANTASTIC_STABLE)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsSorcery(p)) {
+        if (value[0] == BuildingDB(IMPROVE_LIBRARY)
+        || value[0] == BuildingDB(IMPROVE_BEACON_OF_WISDOM)) {
+            burstGold = 30;
+        }
+    } elseif (MomPlayerIsDeath(p)) {
+        if (value[0] == BuildingDB(IMPROVE_BARRACKS)
+        || value[0] == BuildingDB(IMPROVE_MECHANICIANS_GUILD)) {
+            burstGold = 30;
+        }
+    }
+    if (burstGold &gt; 0) {
+        AddGold(p, burstGold);
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MoM sphere event messages (Phase C). Included LAST in the entry-point chain, after</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) 'MomSphereBlessingMessages' post {
+    int_t p;
+    p = player[0];
+    // GrantAdvance does NOT populate advance[], and assigning value[0] into it
+    // does not make it readable -- MEASURED three times now, in three files
+    // (mom_magic.slc, mom_city_effects.slc, and here). value[0] IS the granted
+    // advance index; compare it to AdvanceDB() directly and never touch advance[].
+    if (value[0] != 0 &amp;&amp; IsHumanPlayer(p)) {
+        if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+            Message(g.player, 'MomBlessLife');
+        } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+            Message(g.player, 'MomBlessNature');
+        } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+            Message(g.player, 'MomBlessSorcery');
+        } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+            Message(g.player, 'MomBlessDeath');
+        } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+            Message(g.player, 'MomBlessChaos');
+        }
+    }
+}
+HandleEvent(BeginTurn) 'MomSummonOrderTick' post {
+    int_t p;
+    city_t tmpCity;
+    p = player[0];
+    // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
+    // at spawn time, so the pool is only debited when a creature actually appears.
+    // Re-checking the balance is not redundant with the button-body check: the
+    // only thing that can move the pool between the two is MomMagicPoolTick's
+    // accrual, which is monotonically upward, so a click that was affordable stays
+    // affordable -- but a future spender on the same turn must not be able to push
+    // this negative. The check is a plain comparison at call depth 0.
+    if (p &gt;= 1 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; player[0].cities &gt; 0
+        &amp;&amp; MomMagicCur[p] &gt;= 75) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            MomMagicCur[p] = MomMagicCur[p] - 75;
+            if (IsHumanPlayer(p)) {
+                MomMagicCurDisp = MomMagicCur[p];
+                MomMagicMaxDisp = MomMagicMax[p];
+                MomMagicGenDisp = MomMagicPerTurn[p];
+            }
+            if (p == 1) {
+                CreateUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT), tmpCity.location, 1);
+                Message(p, 'MomSummonGuard');
+            } elseif (p == 2) {
+                CreateUnit(p, UnitDB(UNIT_WARBEARS), tmpCity.location, 1);
+                Message(p, 'MomSummonBear');
+            } elseif (p == 3) {
+                CreateUnit(p, UnitDB(UNIT_MAGE), tmpCity.location, 1);
+                Message(p, 'MomSummonMage');
+            } elseif (p == 4) {
+                CreateUnit(p, UnitDB(UNIT_ZOMBIES), tmpCity.location, 1);
+                Message(p, 'MomSummonZombie');
+            } elseif (p == 5) {
+                CreateUnit(p, UnitDB(UNIT_HELL_HOUNDS), tmpCity.location, 1);
+                Message(p, 'MomSummonHound');
+            }
+        }
+    }
+    // Cleared OUTSIDE the fill condition, not inside it. An order that could not
+    // be filled -- no valid city, or the pool moved below 75 -- must not survive to
+    // re-fire on a later turn, or "it spawned" would no longer pin WHICH turn
+    // consumed the click. Putting this clear inside the gate (as it was before the
+    // cost check existed, when the gate could not fail for a player with a city)
+    // would have made an unaffordable order a permanent standing order.
+    if (p &gt;= 1 &amp;&amp; MomSummonChoice[p] != 0) {
+        MomSummonChoice[p] = 0;
+    }
+}</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>messagebox 'MomMsgSlicAlive' {
+	Show();
+	Text(ID_MOM_MSG_SLIC_ALIVE);
+}
+messagebox 'MomBlessLife' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_LIFE);
+}
+messagebox 'MomBlessNature' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_NATURE);
+}
+messagebox 'MomBlessSorcery' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_SORCERY);
+}
+messagebox 'MomBlessDeath' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_DEATH);
+}
+messagebox 'MomBlessChaos' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_CHAOS);
+}
+// Summon result popups -- one per sphere. A distinct segment per sphere is also
+// what keeps the readout DISCRIMINATING for the harness: the text names the
+// creature, so a single captured frame settles which sphere's branch ran, and no
+// segment is reachable from another sphere's branch. Message(p, 'Key') needs
+// 'Key' to be a DEFINED SEGMENT (see the block comment above) -- adding the
+// scen_str.txt keys alone would have displayed nothing.
+messagebox 'MomSummonGuard' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_GUARD);
+}
+messagebox 'MomSummonBear' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_BEAR);
+}
+messagebox 'MomSummonMage' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_MAGE);
+}
+messagebox 'MomSummonZombie' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_ZOMBIE);
+}
+messagebox 'MomSummonHound' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_HOUND);
+}
+// Insufficient-mana answer for the Summon arm. A messagebox, NOT an alertbox:
+// this fires from inside a button body while the MagicMenu alertbox is being
+// Kill()ed, and stacking a second modal on that path is exactly the shape the
+// harness cannot dismiss. mom_spells.slc's 'MomMsgNoMana' is an alertbox and is
+// deliberately not reused here for that reason -- distinct segment name, so the
+// one-flat-namespace rule is satisfied.
+messagebox 'MomSummonNoMana' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_NOMANA);
+}
+messagebox 'MomMagicPower' {
+	Show();
+	Text(ID_MOM_MSG_MAGIC_POWER);
+}
+// Interactive test: fired directly from keypress.cpp on 'j' (the stock
+// TRIGGER_LIST_KEY_PRESSED path is dead in this build, so C++ executes
+// this segment by name via SlicObject("MagicMenu")).
+// INTERACTIVITY BATTERY (links 5 and 6).
+//
+// Established as of 2026-07-24, do not re-test: input REACHES a button on this
+// surface and the button's SLIC block EXECUTES (links 3+4, proven by clicking
+// Close and watching Kill() run). What that did NOT prove is that a button body
+// can MUTATE state (link 5) and that the mutation PERSISTS and is observable
+// when the box is reopened (link 6) -- Kill() is message lifecycle, not game
+// state, so it can never speak to either.
+//
+// Three arms, each producing a DISTINCT observable so no two outcomes can be
+// confused, exercised ONE PER RUN:
+//   Random   -&gt; sets the display scalar to a sentinel  -&gt; reopen reads "Mana: 42"
+//   Research -&gt; spends 3 from the REAL per-player pool -&gt; reopen reads "Mana: 7"
+//   Goal     -&gt; AddGold, i.e. real ENGINE state        -&gt; HUD gold delta
+// Baseline is "Mana: 10", so 42 / 7 / 10 are mutually exclusive readings.
+//
+// Random vs Research is the load-bearing distinction: MomMagicCurDisp is only a
+// render scalar, so mutating it alone would leave a skeptic room to say nothing
+// in the game model changed. Research writes MomMagicCur[], the actual backing
+// array, and then mirrors it into the scalar purely so the change is visible.
+//
+// Do NOT end a turn between clicking an arm and reopening: MomMagicPoolTick
+// recomputes the Disp scalars every BeginTurn and would overwrite the result,
+// which would look exactly like "the mutation did not persist".
+//
+// Declaration order is safe: MomMagicCur/MomMagicCurDisp live in mom_func.slc,
+// which loads before this file. Nothing here calls into mom_magic.slc, which
+// loads after -- that is what the old "display only" note was guarding against.
+alertbox 'MagicMenu' {
+	Show();
+	Text(ID_MOM_MSG_MAGIC_MENU);
+	// SUMMON: place a summon ORDER. The body only writes a global; the spawn
+	// happens next BeginTurn in MomSummonOrderTick, which resolves the creature
+	// from the caster's own sphere. The body stays assignment-only -- a button
+	// body carries the same nested-call budget as a HandleEvent body (Class 1),
+	// so no user-function calls here, and none are needed: the sphere lookup
+	// belongs at spawn time, not at click time.
+	//
+	// ONE arm as of 2026-07-26, previously two (Guardian / Zombies). The second
+	// arm was link-7 apparatus -- with a single arm "the ordered unit appeared"
+	// could not be told apart from "the handler always spawns that unit" -- and
+	// link 7 is closed. Leaving it in meant every sphere was offered every other
+	// sphere's creature, so a Life tribe could raise zombies. The caption cannot
+	// name the creature (button captions are static string IDs and this segment
+	// is invoked BY NAME from keypress.cpp, so SLIC never gets to pick a
+	// per-sphere variant the way MomSpellShowBook does); the result popup does.
+	// COST 75, checked HERE as well as at spawn time. The click is the moment the
+	// player expects an answer, so an unaffordable click gets an immediate message
+	// rather than a button that appears to do nothing and then produces nothing
+	// next turn. Both branches are comparisons and builtins (Message is a builtin),
+	// so the body is still at call depth 0 -- the Class 1 budget is untouched.
+	Button(ID_MOM_MSG_BTN_SUMMON) {
+		if (MomMagicCur[g.player] &gt;= 75) {
+			MomSummonChoice[g.player] = 1;
+		} else {
+			Message(g.player, 'MomSummonNoMana');
+		}
+		Kill();
+	}
+	// The "Goal" arm (AddGold 500) was REMOVED 2026-07-26 with the same reasoning
+	// as the second summon arm. It existed to prove the SLIC-&gt;engine boundary for
+	// link 5 by writing real engine state that shows on the HUD; that link is
+	// closed, and what remained was a free-money button sitting in the player's
+	// magic menu. The boundary is still exercised in play by the summon path's
+	// CreateUnit, so nothing is lost as evidence.
+	Button(ID_BUTTON_CLOSE) {
+		Kill();
+	}
+}</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>13477</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>// MoM sphere event messages (Phase C). Included LAST in the entry-point chain, after
+// mom_city_effects.slc. Announces each faction's one-time sphere blessing as a popup.
+//
+// Design (source: the original MoM magic-system script at h:\games\ctp2\mom, which
+// popped a "You have chosen the X school of magic!" message on the school-defining
+// advance): the popup fires on the sphere's MAGIC ADVANCE only -- the milestone worth
+// announcing -- NOT on every burst-building completion (that stays quiet gold), so
+// there is no message spam and no flood risk.
+//
+// Plumbing is the base-verified Message(g.player, 'KEY') form + scen_str.txt keys (the
+// momjr NotifyPlayer/ShowMessageBox/inline-string forms are the UNVERIFIED kind and are
+// deliberately not reused). This is a SEPARATE GrantAdvance handler from the blessing-
+// grant handler in mom_city_effects.slc; CTP2 supports multiple handlers per event.
+//
+// No latch is needed: GrantAdvance for a given advance fires once per player, so each
+// blessing message shows once (unlike an unlatched BeginTurn Message, which floods the
+// queue -&gt; 0xC0000005). The IsHumanPlayer guard keeps AI factions' blessings off the
+// human's screen -- you only see your own sphere's blessing.
+HandleEvent(GrantAdvance) 'MomSphereBlessingMessages' post {
+    int_t p;
+    p = player[0];
+    // GrantAdvance does NOT populate advance[], and assigning value[0] into it
+    // does not make it readable -- MEASURED three times now, in three files
+    // (mom_magic.slc, mom_city_effects.slc, and here). value[0] IS the granted
+    // advance index; compare it to AdvanceDB() directly and never touch advance[].
+    if (value[0] != 0 &amp;&amp; IsHumanPlayer(p)) {
+        if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+            Message(g.player, 'MomBlessLife');
+        } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+            Message(g.player, 'MomBlessNature');
+        } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+            Message(g.player, 'MomBlessSorcery');
+        } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+            Message(g.player, 'MomBlessDeath');
+        } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+            Message(g.player, 'MomBlessChaos');
+        }
+    }
+}
+// ---------------------------------------------------------------------------
+// SUMMON CONSUMER: reads the order a MagicMenu arm placed LAST turn, spawns the
+// creature of the CASTER'S OWN SPHERE, and clears the order.
+//
+// Sphere-gated as of 2026-07-26. It used to branch on MomSummonChoice being 1 or
+// 2 and spawn a Guardian Spirit or Zombies accordingly, because the menu offered
+// both to everyone. That was link-7 test scaffolding -- two arms existed only so
+// "the ordered unit appeared" could be told apart from "the handler always
+// summons that unit" -- and once link 7 closed it survived as a Life tribe being
+// able to raise the dead. The order is now a single boolean intent; WHICH
+// creature answers is a property of the caster, not of the button.
+//
+// The sphere IS the player index (1 Life, 2 Nature, 3 Sorcery, 4 Death,
+// 5 Chaos; 0 is barbarians and is excluded by the p &gt;= 1 guard). Seating order
+// is faction identity here -- TRIBES_* are civ-DB record names, not SLIC
+// symbols, so there is nothing else to test against.
+//
+// The mapping is INLINED rather than delegated to MomSphereSummonUnit(), for two
+// independent reasons, either of which alone would force it: scenario.slc
+// includes mom_msg.slc BEFORE mom_magic.slc, so that helper is not yet declared
+// here; and this handler must stay at call depth 0. GetCityByIndex / CityIsValid
+// / CreateUnit / UnitDB / Message are all builtins, so the Class 1 nested-call
+// crash cannot be reached.
+//
+// The 111/222 AddGold sentinels are gone with the scaffolding. They existed
+// because a gold delta on the HUD was easier for the harness to read than a unit
+// sprite; the five distinct result popups now carry that signal, and free gold
+// on every summon was never intended gameplay.
+//
+// player[0] is the turn player -- never player[p], see mom_func.slc.
+// ---------------------------------------------------------------------------
+HandleEvent(BeginTurn) 'MomSummonOrderTick' post {
+    int_t p;
+    city_t tmpCity;
+    p = player[0];
+    // COST 75 (added 2026-07-26). The order is placed at click time and PAID here,
+    // at spawn time, so the pool is only debited when a creature actually appears.
+    // Re-checking the balance is not redundant with the button-body check: the
+    // only thing that can move the pool between the two is MomMagicPoolTick's
+    // accrual, which is monotonically upward, so a click that was affordable stays
+    // affordable -- but a future spender on the same turn must not be able to push
+    // this negative. The check is a plain comparison at call depth 0.
+    if (p &gt;= 1 &amp;&amp; MomSummonChoice[p] != 0 &amp;&amp; player[0].cities &gt; 0
+        &amp;&amp; MomMagicCur[p] &gt;= 75) {
+        GetCityByIndex(player[0], 0, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            MomMagicCur[p] = MomMagicCur[p] - 75;
+            if (IsHumanPlayer(p)) {
+                MomMagicCurDisp = MomMagicCur[p];
+                MomMagicMaxDisp = MomMagicMax[p];
+                MomMagicGenDisp = MomMagicPerTurn[p];
+            }
+            if (p == 1) {
+                CreateUnit(p, UnitDB(UNIT_GUARDIAN_SPIRIT), tmpCity.location, 1);
+                Message(p, 'MomSummonGuard');
+            } elseif (p == 2) {
+                CreateUnit(p, UnitDB(UNIT_WARBEARS), tmpCity.location, 1);
+                Message(p, 'MomSummonBear');
+            } elseif (p == 3) {
+                CreateUnit(p, UnitDB(UNIT_MAGE), tmpCity.location, 1);
+                Message(p, 'MomSummonMage');
+            } elseif (p == 4) {
+                CreateUnit(p, UnitDB(UNIT_ZOMBIES), tmpCity.location, 1);
+                Message(p, 'MomSummonZombie');
+            } elseif (p == 5) {
+                CreateUnit(p, UnitDB(UNIT_HELL_HOUNDS), tmpCity.location, 1);
+                Message(p, 'MomSummonHound');
+            }
+        }
+    }
+    // Cleared OUTSIDE the fill condition, not inside it. An order that could not
+    // be filled -- no valid city, or the pool moved below 75 -- must not survive to
+    // re-fire on a later turn, or "it spawned" would no longer pin WHICH turn
+    // consumed the click. Putting this clear inside the gate (as it was before the
+    // cost check existed, when the gate could not fail for a player with a city)
+    // would have made an unaffordable order a permanent standing order.
+    if (p &gt;= 1 &amp;&amp; MomSummonChoice[p] != 0) {
+        MomSummonChoice[p] = 0;
+    }
+}
+// ---------------------------------------------------------------------------
+// MESSAGEBOX SEGMENTS (engine ground truth, slicfunc.cpp Slic_Message::Call):
+// Message(player, 'Key') requires 'Key' to be a DEFINED SEGMENT -- with no
+// messagebox block the call fails SFN_ERROR_NOT_SEGMENT and NOTHING displays.
+// The scen_str.txt keys alone were never enough; these blocks are the missing
+// half. Base-verified form (script.slc): Show() pops the window immediately,
+// Text(ID_&lt;key&gt;) resolves the string DB key verbatim (tut2 convention:
+// Text(ID_T_TURN_0) &lt;-&gt; tut2_str.txt key T_TURN_0). MessageType is optional
+// (24 base messageboxes omit it) and is deliberately omitted here.
+// ---------------------------------------------------------------------------
+messagebox 'MomMsgSlicAlive' {
+	Show();
+	Text(ID_MOM_MSG_SLIC_ALIVE);
+}
+messagebox 'MomBlessLife' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_LIFE);
+}
+messagebox 'MomBlessNature' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_NATURE);
+}
+messagebox 'MomBlessSorcery' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_SORCERY);
+}
+messagebox 'MomBlessDeath' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_DEATH);
+}
+messagebox 'MomBlessChaos' {
+	Show();
+	Text(ID_MOM_MSG_BLESS_CHAOS);
+}
+// Summon result popups -- one per sphere. A distinct segment per sphere is also
+// what keeps the readout DISCRIMINATING for the harness: the text names the
+// creature, so a single captured frame settles which sphere's branch ran, and no
+// segment is reachable from another sphere's branch. Message(p, 'Key') needs
+// 'Key' to be a DEFINED SEGMENT (see the block comment above) -- adding the
+// scen_str.txt keys alone would have displayed nothing.
+messagebox 'MomSummonGuard' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_GUARD);
+}
+messagebox 'MomSummonBear' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_BEAR);
+}
+messagebox 'MomSummonMage' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_MAGE);
+}
+messagebox 'MomSummonZombie' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_ZOMBIE);
+}
+messagebox 'MomSummonHound' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_HOUND);
+}
+// Insufficient-mana answer for the Summon arm. A messagebox, NOT an alertbox:
+// this fires from inside a button body while the MagicMenu alertbox is being
+// Kill()ed, and stacking a second modal on that path is exactly the shape the
+// harness cannot dismiss. mom_spells.slc's 'MomMsgNoMana' is an alertbox and is
+// deliberately not reused here for that reason -- distinct segment name, so the
+// one-flat-namespace rule is satisfied.
+messagebox 'MomSummonNoMana' {
+	Show();
+	Text(ID_MOM_MSG_SUMMON_NOMANA);
+}
+messagebox 'MomMagicPower' {
+	Show();
+	Text(ID_MOM_MSG_MAGIC_POWER);
+}
+// Interactive test: fired directly from keypress.cpp on 'j' (the stock
+// TRIGGER_LIST_KEY_PRESSED path is dead in this build, so C++ executes
+// this segment by name via SlicObject("MagicMenu")).
+// INTERACTIVITY BATTERY (links 5 and 6).
+//
+// Established as of 2026-07-24, do not re-test: input REACHES a button on this
+// surface and the button's SLIC block EXECUTES (links 3+4, proven by clicking
+// Close and watching Kill() run). What that did NOT prove is that a button body
+// can MUTATE state (link 5) and that the mutation PERSISTS and is observable
+// when the box is reopened (link 6) -- Kill() is message lifecycle, not game
+// state, so it can never speak to either.
+//
+// Three arms, each producing a DISTINCT observable so no two outcomes can be
+// confused, exercised ONE PER RUN:
+//   Random   -&gt; sets the display scalar to a sentinel  -&gt; reopen reads "Mana: 42"
+//   Research -&gt; spends 3 from the REAL per-player pool -&gt; reopen reads "Mana: 7"
+//   Goal     -&gt; AddGold, i.e. real ENGINE state        -&gt; HUD gold delta
+// Baseline is "Mana: 10", so 42 / 7 / 10 are mutually exclusive readings.
+//
+// Random vs Research is the load-bearing distinction: MomMagicCurDisp is only a
+// render scalar, so mutating it alone would leave a skeptic room to say nothing
+// in the game model changed. Research writes MomMagicCur[], the actual backing
+// array, and then mirrors it into the scalar purely so the change is visible.
+//
+// Do NOT end a turn between clicking an arm and reopening: MomMagicPoolTick
+// recomputes the Disp scalars every BeginTurn and would overwrite the result,
+// which would look exactly like "the mutation did not persist".
+//
+// Declaration order is safe: MomMagicCur/MomMagicCurDisp live in mom_func.slc,
+// which loads before this file. Nothing here calls into mom_magic.slc, which
+// loads after -- that is what the old "display only" note was guarding against.
+alertbox 'MagicMenu' {
+	Show();
+	Text(ID_MOM_MSG_MAGIC_MENU);
+	// SUMMON: place a summon ORDER. The body only writes a global; the spawn
+	// happens next BeginTurn in MomSummonOrderTick, which resolves the creature
+	// from the caster's own sphere. The body stays assignment-only -- a button
+	// body carries the same nested-call budget as a HandleEvent body (Class 1),
+	// so no user-function calls here, and none are needed: the sphere lookup
+	// belongs at spawn time, not at click time.
+	//
+	// ONE arm as of 2026-07-26, previously two (Guardian / Zombies). The second
+	// arm was link-7 apparatus -- with a single arm "the ordered unit appeared"
+	// could not be told apart from "the handler always spawns that unit" -- and
+	// link 7 is closed. Leaving it in meant every sphere was offered every other
+	// sphere's creature, so a Life tribe could raise zombies. The caption cannot
+	// name the creature (button captions are static string IDs and this segment
+	// is invoked BY NAME from keypress.cpp, so SLIC never gets to pick a
+	// per-sphere variant the way MomSpellShowBook does); the result popup does.
+	// COST 75, checked HERE as well as at spawn time. The click is the moment the
+	// player expects an answer, so an unaffordable click gets an immediate message
+	// rather than a button that appears to do nothing and then produces nothing
+	// next turn. Both branches are comparisons and builtins (Message is a builtin),
+	// so the body is still at call depth 0 -- the Class 1 budget is untouched.
+	Button(ID_MOM_MSG_BTN_SUMMON) {
+		if (MomMagicCur[g.player] &gt;= 75) {
+			MomSummonChoice[g.player] = 1;
+		} else {
+			Message(g.player, 'MomSummonNoMana');
+		}
+		Kill();
+	}
+	// The "Goal" arm (AddGold 500) was REMOVED 2026-07-26 with the same reasoning
+	// as the second summon arm. It existed to prove the SLIC-&gt;engine boundary for
+	// link 5 by writing real engine state that shows on the HUD; that link is
+	// closed, and what remained was a free-money button sitting in the player's
+	// magic menu. The boundary is still exercised in play by the summon path's
+	// CreateUnit, so nothing is lost as evidence.
+	Button(ID_BUTTON_CLOSE) {
+		Kill();
+	}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>mom_magic.slc</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MoM magic system (M1-M4) -- reconstructed from session log after H: FS corruption.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>int_f MomRecalcMagicPerTurn(int_t mp_1)
+{
+    int_t i;
+    int_t j;
+    int_t gen;
+    int_t pct;
+    int_t nodes;
+    city_t tmpCity;
+    location_t cloc;
+    location_t nloc;
+    gen = 10;
+    nodes = 0;
+    // NEVER player[mp_1]: player[N] indexes the event ARG array (size 1), so mp_1&gt;=1
+    // throws "Array index 1 out of bounds". The turn player is player[0].
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            gen = gen + tmpCity.population * 2;
+            // M4 mana nodes: good-bearing tiles in the city inner radius (center + 8 neighbors).
+            cloc = tmpCity.location;
+            if (HasGood(cloc) &gt;= 0) {
+                nodes = nodes + 1;
+            }
+            // GetNeighbor's return value MUST gate the read of its out-arg.
+            // At a map edge it returns 0 and does NOT write nloc, so the
+            // ungated form below fed HasGood() an uninitialised location_t --
+            // a hard 0xC0000005, no SLIC error dialog, because it is a bad
+            // pointer inside a builtin rather than a SLIC diagnostic. It is the
+            // same defect already fixed in MomSpawnSphereUnit (mom_func.slc) on
+            // 2026-07-25 -- that fix was applied at one call site and missed
+            // this one.
+            //
+            // CORRECTION 2026-07-26: an earlier version of this comment claimed
+            // this gate explained the found-a-city end-turn 0xC0000005. That is
+            // FALSIFIED -- the crash survived this fix, survived neutering all
+            // four MoM BeginTurn handlers, and survived disabling every scenario
+            // SLIC include. This is a real latent defect on the map edge, and
+            // nothing more. Do not re-attribute the end-turn crash to it.
+            for (j = 0; j &lt; 8; j = j + 1) {
+                if (GetNeighbor(cloc, j, nloc)) {
+                    if (HasGood(nloc) &gt;= 0) {
+                        nodes = nodes + 1;
+                    }
+                }
+            }
+        }
+    }
+    gen = gen + nodes * 5;   // MANA_NODE_BONUS = 5 per node, before school scaling
+    pct = MomMagicSchoolPct[mp_1];
+    if (pct == 0) {
+        pct = 100;
+    }
+    gen = gen * pct / 100;
+    return gen;
+}</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) 'MomMagicPoolTick' post {
+    int_t p;
+    p = player[0];
+    // CRASH FIX (turn-10): magic is for sphere players 1..5 only. Player 0 (barbarians) and
+    // any non-sphere player must skip. SLIC 'post' handlers cannot bare-return, so gate the
+    // whole body with an if (this handler running for player 0 was the turn-10 crash).
+    if (p &gt;= 1) {
+        if (MomMagicMax[p] == 0) {
+            MomMagicMax[p] = 100;
+        }
+        MomMagicPerTurn[p] = MomRecalcMagicPerTurn(p);
+        MomMagicCur[p] = MomMagicCur[p] + MomMagicPerTurn[p];
+        if (MomMagicCur[p] &gt; MomMagicMax[p]) {
+            MomMagicCur[p] = MomMagicMax[p];
+        }
+        // M3 pool-overflow auto-summon: REMOVED 2026-07-26. It zeroed the pool the
+        // moment it capped, so mana could never sit at the cap and the 50/100-cost
+        // workings in mom_spells.slc were unreachable by construction -- the pool
+        // was a sawtooth, not a resource. The pool now simply clamps at max and the
+        // player spends it deliberately (Summon 75, Flame Strike 50, Demon 100).
+        // MomSphereSummonUnit() existed only to serve this block and is gone too;
+        // the same mapping is inlined at each spend site for the Class-1 nested-call
+        // budget (see mom_spells.slc:41).
+        // Refresh the display scalars EVERY turn so the 'j' magic menu
+        // (alertbox 'MagicMenu') always shows current values, not just on
+        // the 10-round popup cadence below.
+        if (IsHumanPlayer(p)) {
+            MomMagicCurDisp = MomMagicCur[p];
+            MomMagicMaxDisp = MomMagicMax[p];
+            MomMagicGenDisp = MomMagicPerTurn[p];
+        }
+        // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
+        //
+        // Redundant: the display scalars are refreshed EVERY turn just above, so
+        // the 'j' MagicMenu alertbox already reports current values on demand.
+        // Harmful: a Message window is an aui surface and aui polls GetCursorPos,
+        // so a posted click can never close one -- it stayed pinned over the
+        // top-left of the map from round 0 onward, and each dismissal attempt fell
+        // through onto the map and scrolled the view. Status belongs on the
+        // alertbox, which both a human and the harness can actually dismiss.
+        // MomMagicShownTurn[] is left declared -- it is the re-entry latch idiom
+        // and a school popup may want it again.
+    }
+}
+// M2 school multipliers -- set the player's per-turn multiplier + pool cap on their sphere's
+// magic advance. Separate named GrantAdvance handler (coexists with blessing handlers).
+HandleEvent(GrantAdvance) 'MomMagicSchoolGrant' post {
+    int_t p;
+    int_t granted;
+    p = player[0];
+    granted = 0;
+    // MEASURED 2026-07-25, twice. GrantAdvance does NOT populate advance[], so
+    // reading advance[0].type is "Array index 0 out of bounds". The first fix
+    // copied value[0] into advance[0] first (the idiom the sibling handler in
+    // mom_city_effects.slc used) -- that ALSO errored, at the same line, which
+    // falsified it: the assignment does not make advance[0] readable. The
+    // granted advance IS value[0], an advance index, directly comparable to
+    // AdvanceDB(). The advance[] array is not used at all now.
+    if (value[0] != 0) {
+    if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+        MomMagicSchoolPct[p] = 100;
+        MomMagicMax[p] = 200;
+        granted = 1;
+    } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+        MomMagicSchoolPct[p] = 110;
+        MomMagicMax[p] = 220;
+        granted = 1;
+    } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+        MomMagicSchoolPct[p] = 125;
+        MomMagicMax[p] = 260;
+        granted = 1;
+    } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+        MomMagicSchoolPct[p] = 115;
+        MomMagicMax[p] = 240;
+        granted = 1;
+    } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+        MomMagicSchoolPct[p] = 140;
+        MomMagicMax[p] = 300;
+        granted = 1;
+    }
+    if (granted &amp;&amp; IsHumanPlayer(p)) {
+        MomMagicPerTurn[p] = MomRecalcMagicPerTurn(p);
+        MomMagicCurDisp = MomMagicCur[p];
+        MomMagicMaxDisp = MomMagicMax[p];
+        MomMagicGenDisp = MomMagicPerTurn[p];
+        Message(g.player, 'MomMagicPower');
+    }
+    }   // advance[0] != 0
+}</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7756</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>// MoM magic system (M1-M4) -- reconstructed from session log after H: FS corruption.
+// #included LAST in scenario.slc, after mom_msg.slc. Base-verified SLIC only.
+// M1 per-player magic-power pool, M2 school multipliers, M3 pool-overflow summon,
+// M4 mana nodes. Popup uses base-verified {scalar} interpolation (NOT {Arr[Idx]}).
+// NOTE: includes the sphere-guard crash fix (p &lt; 1 return) that was in progress when
+// the filesystem corrupted -- the turn-10 crash was this handler running for player 0.
+// (magic power declarations live in mom_func.slc -- loaded first)
+int_f MomRecalcMagicPerTurn(int_t mp_1)
+{
+    int_t i;
+    int_t j;
+    int_t gen;
+    int_t pct;
+    int_t nodes;
+    city_t tmpCity;
+    location_t cloc;
+    location_t nloc;
+    gen = 10;
+    nodes = 0;
+    // NEVER player[mp_1]: player[N] indexes the event ARG array (size 1), so mp_1&gt;=1
+    // throws "Array index 1 out of bounds". The turn player is player[0].
+    for (i = 0; i &lt; player[0].cities; i = i + 1) {
+        GetCityByIndex(player[0], i, tmpCity);
+        if (CityIsValid(tmpCity)) {
+            gen = gen + tmpCity.population * 2;
+            // M4 mana nodes: good-bearing tiles in the city inner radius (center + 8 neighbors).
+            cloc = tmpCity.location;
+            if (HasGood(cloc) &gt;= 0) {
+                nodes = nodes + 1;
+            }
+            // GetNeighbor's return value MUST gate the read of its out-arg.
+            // At a map edge it returns 0 and does NOT write nloc, so the
+            // ungated form below fed HasGood() an uninitialised location_t --
+            // a hard 0xC0000005, no SLIC error dialog, because it is a bad
+            // pointer inside a builtin rather than a SLIC diagnostic. It is the
+            // same defect already fixed in MomSpawnSphereUnit (mom_func.slc) on
+            // 2026-07-25 -- that fix was applied at one call site and missed
+            // this one.
+            //
+            // CORRECTION 2026-07-26: an earlier version of this comment claimed
+            // this gate explained the found-a-city end-turn 0xC0000005. That is
+            // FALSIFIED -- the crash survived this fix, survived neutering all
+            // four MoM BeginTurn handlers, and survived disabling every scenario
+            // SLIC include. This is a real latent defect on the map edge, and
+            // nothing more. Do not re-attribute the end-turn crash to it.
+            for (j = 0; j &lt; 8; j = j + 1) {
+                if (GetNeighbor(cloc, j, nloc)) {
+                    if (HasGood(nloc) &gt;= 0) {
+                        nodes = nodes + 1;
+                    }
+                }
+            }
+        }
+    }
+    gen = gen + nodes * 5;   // MANA_NODE_BONUS = 5 per node, before school scaling
+    pct = MomMagicSchoolPct[mp_1];
+    if (pct == 0) {
+        pct = 100;
+    }
+    gen = gen * pct / 100;
+    return gen;
+}
+// MomSphereSummonUnit() was REMOVED 2026-07-26 along with its only caller, the
+// pool-overflow auto-summon below. The sphere -&gt; creature mapping now lives
+// inlined at each spend site (mom_msg.slc MomSummonOrderTick, mom_spells.slc
+// MomCastFlameStrike), which is where the Class-1 nested-call budget requires
+// it anyway -- so nothing was lost but a level of indirection.
+HandleEvent(BeginTurn) 'MomMagicPoolTick' post {
+    int_t p;
+    p = player[0];
+    // CRASH FIX (turn-10): magic is for sphere players 1..5 only. Player 0 (barbarians) and
+    // any non-sphere player must skip. SLIC 'post' handlers cannot bare-return, so gate the
+    // whole body with an if (this handler running for player 0 was the turn-10 crash).
+    if (p &gt;= 1) {
+        if (MomMagicMax[p] == 0) {
+            MomMagicMax[p] = 100;
+        }
+        MomMagicPerTurn[p] = MomRecalcMagicPerTurn(p);
+        MomMagicCur[p] = MomMagicCur[p] + MomMagicPerTurn[p];
+        if (MomMagicCur[p] &gt; MomMagicMax[p]) {
+            MomMagicCur[p] = MomMagicMax[p];
+        }
+        // M3 pool-overflow auto-summon: REMOVED 2026-07-26. It zeroed the pool the
+        // moment it capped, so mana could never sit at the cap and the 50/100-cost
+        // workings in mom_spells.slc were unreachable by construction -- the pool
+        // was a sawtooth, not a resource. The pool now simply clamps at max and the
+        // player spends it deliberately (Summon 75, Flame Strike 50, Demon 100).
+        // MomSphereSummonUnit() existed only to serve this block and is gone too;
+        // the same mapping is inlined at each spend site for the Class-1 nested-call
+        // budget (see mom_spells.slc:41).
+        // Refresh the display scalars EVERY turn so the 'j' magic menu
+        // (alertbox 'MagicMenu') always shows current values, not just on
+        // the 10-round popup cadence below.
+        if (IsHumanPlayer(p)) {
+            MomMagicCurDisp = MomMagicCur[p];
+            MomMagicMaxDisp = MomMagicMax[p];
+            MomMagicGenDisp = MomMagicPerTurn[p];
+        }
+        // Periodic popup every 10 rounds: REMOVED 2026-07-25, redundant and harmful.
+        //
+        // Redundant: the display scalars are refreshed EVERY turn just above, so
+        // the 'j' MagicMenu alertbox already reports current values on demand.
+        // Harmful: a Message window is an aui surface and aui polls GetCursorPos,
+        // so a posted click can never close one -- it stayed pinned over the
+        // top-left of the map from round 0 onward, and each dismissal attempt fell
+        // through onto the map and scrolled the view. Status belongs on the
+        // alertbox, which both a human and the harness can actually dismiss.
+        // MomMagicShownTurn[] is left declared -- it is the re-entry latch idiom
+        // and a school popup may want it again.
+    }
+}
+// M2 school multipliers -- set the player's per-turn multiplier + pool cap on their sphere's
+// magic advance. Separate named GrantAdvance handler (coexists with blessing handlers).
+HandleEvent(GrantAdvance) 'MomMagicSchoolGrant' post {
+    int_t p;
+    int_t granted;
+    p = player[0];
+    granted = 0;
+    // MEASURED 2026-07-25, twice. GrantAdvance does NOT populate advance[], so
+    // reading advance[0].type is "Array index 0 out of bounds". The first fix
+    // copied value[0] into advance[0] first (the idiom the sibling handler in
+    // mom_city_effects.slc used) -- that ALSO errored, at the same line, which
+    // falsified it: the assignment does not make advance[0] readable. The
+    // granted advance IS value[0], an advance index, directly comparable to
+    // AdvanceDB(). The advance[] array is not used at all now.
+    if (value[0] != 0) {
+    if (MomPlayerIsLife(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_LIFE_MAGIC)) {
+        MomMagicSchoolPct[p] = 100;
+        MomMagicMax[p] = 200;
+        granted = 1;
+    } elseif (MomPlayerIsNature(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_NATURE_MAGIC)) {
+        MomMagicSchoolPct[p] = 110;
+        MomMagicMax[p] = 220;
+        granted = 1;
+    } elseif (MomPlayerIsSorcery(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_SORCERY)) {
+        MomMagicSchoolPct[p] = 125;
+        MomMagicMax[p] = 260;
+        granted = 1;
+    } elseif (MomPlayerIsDeath(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_DEATH_MAGIC)) {
+        MomMagicSchoolPct[p] = 115;
+        MomMagicMax[p] = 240;
+        granted = 1;
+    } elseif (MomPlayerIsChaos(p) &amp;&amp; value[0] == AdvanceDB(ADVANCE_CHAOS_MAGIC)) {
+        MomMagicSchoolPct[p] = 140;
+        MomMagicMax[p] = 300;
+        granted = 1;
+    }
+    if (granted &amp;&amp; IsHumanPlayer(p)) {
+        MomMagicPerTurn[p] = MomRecalcMagicPerTurn(p);
+        MomMagicCurDisp = MomMagicCur[p];
+        MomMagicMaxDisp = MomMagicMax[p];
+        MomMagicGenDisp = MomMagicPerTurn[p];
+        Message(g.player, 'MomMagicPower');
+    }
+    }   // advance[0] != 0
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>MoM spellcasting layer (Phase D) -- imports the momjr-source spell features</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>// Flame Strike: any sphere; projects the caster's sphere creature at the
+// nearest enemy city. Cost 50.
+//
+// FLAT ON PURPOSE -- do not "clean this up" by calling MomSphereSummonUnit and
+// MomCastAtNearestEnemy. MEASURED 2026-07-25 (bisect, casts disabled = 25-turn
+// run survives, casts enabled = 0xC0000005 with no SLIC error dialog): a Button
+// or trigger body gets ONE level of user call, and that callee must not call
+// another user function. HandleEvent bodies are more generous -- mom_magic's
+// BeginTurn goes handler -&gt; MomSphereSummonUnit -&gt; MomPlayerIsLife every turn
+// without incident -- so the budget is per ENTRY POINT, not global. The sphere
+// lookup (mom_magic.slc:52) and the targeting scan (MomCastAtNearestEnemy above)
+// are therefore inlined here.
+void_f MomCastFlameStrike(int_t p)
+{
+    int_t i;
+    int_t j;
+    int_t best;
+    int_t d;
+    int_t found;
+    int_t summon;
+    city_t homeCity;
+    city_t tmpCity;
+    location_t homeLoc;
+    location_t bestLoc;
+    if (p &gt;= 1) {
+        if (MomMagicCur[p] &lt; 50) {
+            if (IsHumanPlayer(p)) {
+                Message(g.player, 'MomMsgNoMana');
+            }
+        } else {
+            // inlined MomSphereSummonUnit: seating is player N == civ N
+            summon = 0;
+            if (p == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
+            if (p == 2) { summon = UnitDB(UNIT_WARBEARS); }
+            if (p == 3) { summon = UnitDB(UNIT_MAGE); }
+            if (p == 4) { summon = UnitDB(UNIT_ZOMBIES); }
+            if (p == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
+            // inlined MomCastAtNearestEnemy(p, summon, 50, 0)
+            found = 0;
+            best = 999999;
+            if (player[0].cities &gt; 0 &amp;&amp; summon != 0) {
+                GetCityByIndex(player[0], 0, homeCity);
+                if (CityIsValid(homeCity)) {
+                    homeLoc = homeCity.location;
+                    // MEASURED 2026-07-25: assigning player[2] = i for every i in
+                    // 1..30 and then reading .cities dereferences player slots that
+                    // do not exist -- a deterministic 0xC0000005 the first time this
+                    // scan runs. This is reached from MomSpellAICast at &gt;= 75% pool,
+                    // which is why every headless run died at turn 7 with a clean
+                    // hook log and no SLIC error. IsPlayerAlive is base-verified
+                    // (present in ctp2.exe, used throughout AlexanderTheGreat) and is
+                    // a BUILTIN, so it costs nothing against the nested-call budget.
+                    for (i = 1; i &lt; 31; i = i + 1) {
+                        if (i != p &amp;&amp; IsPlayerAlive(i)) {
+                        player[2] = i;
+                        if (player[2].cities &gt; 0) {
+                            for (j = 0; j &lt; player[2].cities; j = j + 1) {
+                                GetCityByIndex(player[2], j, tmpCity);
+                                if (CityIsValid(tmpCity)) {
+                                    d = Distance(homeLoc, tmpCity.location);
+                                    if (d &lt; best) {
+                                        best = d;
+                                        bestLoc = tmpCity.location;
+                                        found = 1;
+                                    }
+                                }
+                            }
+                        }
+                        }
+                    }
+                    if (found == 1) {
+                        MomMagicCur[p] = MomMagicCur[p] - 50;
+                        CreateUnit(p, summon, bestLoc, 2);
+                        if (IsHumanPlayer(p)) {
+                            MomSpellCurDisp = MomMagicCur[p];
+                            MomSpellMaxDisp = MomMagicMax[p];
+                            Message(g.player, 'MomMsgFlameCast');
+                        }
+                    } else {
+                        if (IsHumanPlayer(p)) {
+                            Message(g.player, 'MomMsgNoTarget');
+                        }
+                    }
+                }
+            }
+        }
+    }
+}
+// Demon Strike: Chaos school only (original rule). Cost 100.
+void_f MomCastDemonStrike(int_t p)
+{
+    int_t i;
+    int_t j;
+    int_t best;
+    int_t d;
+    int_t found;
+    city_t homeCity;
+    city_t tmpCity;
+    location_t homeLoc;
+    location_t bestLoc;
+    if (p &gt;= 1) {
+        // Inlined (p == 5) rather than MomPlayerIsChaos(p): this runs from a
+        // Button body, and a nested user call on that path is the measured
+        // 0xC0000005 documented in MomSpellShowBook below.
+        if (p != 5) {
+            if (IsHumanPlayer(p)) {
+                Message(g.player, 'MomMsgNotChaos');
+            }
+        } else {
+            if (MomMagicCur[p] &lt; 100) {
+                if (IsHumanPlayer(p)) {
+                    Message(g.player, 'MomMsgNoMana');
+                }
+            } else {
+                // Flat for the same reason as MomCastFlameStrike -- see the note
+                // there. This is reached from a Button body.
+                found = 0;
+                best = 999999;
+                if (player[0].cities &gt; 0) {
+                    GetCityByIndex(player[0], 0, homeCity);
+                    if (CityIsValid(homeCity)) {
+                        homeLoc = homeCity.location;
+                        // Same dead-player-slot guard as MomCastFlameStrike above.
+                        for (i = 1; i &lt; 31; i = i + 1) {
+                            if (i != p &amp;&amp; IsPlayerAlive(i)) {
+                            player[2] = i;
+                            if (player[2].cities &gt; 0) {
+                                for (j = 0; j &lt; player[2].cities; j = j + 1) {
+                                    GetCityByIndex(player[2], j, tmpCity);
+                                    if (CityIsValid(tmpCity)) {
+                                        d = Distance(homeLoc, tmpCity.location);
+                                        if (d &lt; best) {
+                                            best = d;
+                                            bestLoc = tmpCity.location;
+                                            found = 1;
+                                        }
+                                    }
+                                }
+                            }
+                            }
+                        }
+                        if (found == 1) {
+                            MomMagicCur[p] = MomMagicCur[p] - 100;
+                            CreateUnit(p, UnitDB(UNIT_DEMON), bestLoc, 2);
+                            if (IsHumanPlayer(p)) {
+                                MomSpellCurDisp = MomMagicCur[p];
+                                MomSpellMaxDisp = MomMagicMax[p];
+                                Message(g.player, 'MomMsgDemonCast');
+                            }
+                        } else {
+                            if (IsHumanPlayer(p)) {
+                                Message(g.player, 'MomMsgNoTarget');
+                            }
+                        }
+                    }
+                }
+            }
+        }
+    }
+}
+// Show the spellbook popup for player p (pool status + cast buttons).
+void_f MomSpellShowBook(int_t p)
+{
+    if (p &gt;= 1) {
+        MomSpellCurDisp = MomMagicCur[p];
+        MomSpellMaxDisp = MomMagicMax[p];
+        // NESTED USER-FUNCTION CALLS CRASH ON THE TRIGGER PATH (measured
+        // 2026-07-25, three runs, one variable each):
+        //   trigger -&gt; inline Message                       = OK
+        //   trigger -&gt; MomSpellShowBook -&gt; Message          = OK
+        //   trigger -&gt; MomSpellShowBook -&gt; MomPlayerIsChaos = 0xC0000005
+        // One level of user call from a trigger body is fine; a SECOND level is
+        // not. No SLIC error dialog -- the process dies. An explicit `== 1`
+        // comparison does NOT help; the crash is the nested call itself, not the
+        // truthiness form. MomPlayerIsChaos is just `p == 5` (mom_func.slc:49),
+        // so inline the comparison here rather than call it. Any other helper
+        // reached from a trigger or Button body needs the same treatment.
+        if (p == 5) {
+            Message(g.player, 'MomMsgSpellbookChaos');
+        } else {
+            Message(g.player, 'MomMsgSpellbook');
+        }
+    }
+}</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>// Player spellbook: offered once each time the pool crosses 60% of max
+// (re-armed when it drops back below). Chaos gets the extra Demon button.
+// (On-demand access will come from the Ritual Circle trigger improvement.)
+HandleEvent(BeginTurn) 'MomSpellMenuTick' post {
+    int_t p;
+    int_t threshold;
+    p = player[0];
+    // TEMP PROBE REMOVED 2026-07-25. It called MomSpellShowBook unconditionally
+    // every BeginTurn, so its Message stacked on mom_magic's own BeginTurn
+    // message in the same event. MEASURED: 2/2 runs crashed (game window gone,
+    // no crash.txt) with this handler enabled and 2/2 passed with it disabled;
+    // the other two entry points (MomSpellAICast, the MagicButton trigger) were
+    // cleared by the same bisect. This is the queue-flood class already
+    // documented at scenario.slc:33 -- an unlatched Message in BeginTurn floods
+    // the queue -&gt; 0xC0000005. The threshold logic below is correctly latched
+    // (MomSpellPromptArmed re-arms only after the pool drops back under 60%),
+    // which is why it is safe to keep.
+    if (p &gt;= 1 &amp;&amp; IsHumanPlayer(p) &amp;&amp; MomMagicMax[p] &gt; 0) {
+        threshold = (MomMagicMax[p] * 3) / 5;
+        if (MomMagicCur[p] &lt; threshold) {
+            MomSpellPromptArmed[p] = 1;
+        }
+        if (MomSpellPromptArmed[p] == 1 &amp;&amp; MomMagicCur[p] &gt;= threshold) {
+            MomSpellPromptArmed[p] = 0;
+            // AUTO-POPUP REMOVED 2026-07-25. Latched or not, this put a MODAL on
+            // screen at BeginTurn on top of mom_magic's own status box. Unread SLIC
+            // messages QUEUE, they do not replace each other, so from the first
+            // crossing onward every turn starts with two stacked modals; the
+            // end-turn click lands on a box instead of the button and the
+            // playthrough stalls (measured: TURN_DID_NOT_ADVANCE_AT_6). Blind-
+            // dismissing them is worse -- the fixed close coordinate lands on a
+            // CAST button on this box, firing a spell nobody asked for. The
+            // spellbook is on-demand only now, via the 'MomOpenSpellbook' trigger
+            // below (verified headless: MagicButton -&gt; SPELLBOOK alertbox).
+            // The latch bookkeeping above is kept so a future opt-in re-arm still
+            // has correct state.
+        }
+    }
+}
+// AI spellcasting (the momjr original gated at 75% of max but its targeting
+// was a placeholder that never found a target): at &gt;= 75% pool the AI casts
+// for real -- Chaos AIs prefer Demon Strike, everyone else Flame Strike.
+HandleEvent(BeginTurn) 'MomSpellAICast' post {
+    int_t p;
+    p = player[0];
+    if (p &gt;= 1 &amp;&amp; IsHumanPlayer(p) == 0 &amp;&amp; MomMagicMax[p] &gt; 0) {
+        if (MomMagicCur[p] * 4 &gt;= MomMagicMax[p] * 3) {
+            // Inlined chaos test -- see MomSpellShowBook for the nested-call crash.
+            if (p == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
+                MomCastDemonStrike(p);
+            } else {
+                MomCastFlameStrike(p);
+            }
+        }
+    }
+}</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>// On-demand access: a native SLIC UI-component trigger, NOT a keypress.
+// REVERTED (2026-07-18): the keyboard path (SetActionKey/RunKeyboardTrigger
+// ActionKey&lt;N&gt; dispatch, an engine C++ patch) worked mechanically but froze
+// the game on first real test, AND 'm' collides with the base game's own
+// keymap.txt binding (m -&gt; MOVE_ORDER) -- a real player loses unit-move
+// orders for as long as this scenario is loaded. No engine patch needed for
+// this at all: `trigger 'X' on "LDL.Control.Path" when(cond) {...}` is a
+// standard, ALREADY-WORKING SLIC mechanism (fires via
+// HandleGameSpecificLeftClick -&gt; SlicEngine::RunUITriggers for any
+// LDL-defined clickable control; 15+ proven examples in base
+// ctp2_data/default/gamedata/tut2_main.slc, e.g. 'TSPScience' on
+// "ControlPanelWindow.ControlPanel.ShortcutPad.ScienceButton"). Event-driven
+// (fires once per real click) and repeatable (omitting DisableTrigger(), as
+// the base one-shot tutorial triggers deliberately call it and we don't).
+trigger 'MomOpenSpellbook' on "ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton" when (1) {
+    MomSpellShowBook(g.player);
+}</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>alertbox 'MomMsgSpellbook' {
+    Show();
+    Text(ID_MOM_MSG_SPELLBOOK);
+    Button(ID_BUTTON_RESEARCH) {
+        MomCastFlameStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+}
+alertbox 'MomMsgSpellbookChaos' {
+    Show();
+    Text(ID_MOM_MSG_SPELLBOOK);
+    Button(ID_BUTTON_GOAL) {
+        MomCastDemonStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_RESEARCH) {
+        MomCastFlameStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+}
+alertbox 'MomMsgDemonCast' {
+    Show();
+    Text(ID_MOM_MSG_DEMON_CAST);
+}
+alertbox 'MomMsgFlameCast' {
+    Show();
+    Text(ID_MOM_MSG_FLAME_CAST);
+}
+alertbox 'MomMsgNoTarget' {
+    Show();
+    Text(ID_MOM_MSG_NO_TARGET);
+}
+alertbox 'MomMsgNoMana' {
+    Show();
+    Text(ID_MOM_MSG_NO_MANA);
+}
+alertbox 'MomMsgNotChaos' {
+    Show();
+    Text(ID_MOM_MSG_NOT_CHAOS);
+}</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>15883</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>// MoM spellcasting layer (Phase D) -- imports the momjr-source spell features
+// (Demon Strike, Flame Strike, on-demand magic info, AI spellcasting) onto
+// base-verified plumbing. #included from scenario.slc AFTER mom_magic.slc.
+//
+// FIDELITY NOTE (engine ground truth): the momjr original bound spells to
+// HandleEvent(KeyPress) with g.key -- that event DOES NOT EXIST in this
+// engine, and TRIGGER_LIST_KEY_PRESSED has zero subscribers engine-wide
+// (SlicEngine.cpp: dead machinery), so the original's keypress casting could
+// never have fired. The importable feature is the SPELL, not the key:
+//   - player casting = spellbook choice popup (messagebox Buttons, the tut2
+//     base-verified form) offered when the mana pool crosses 60% of max
+//   - targeting = nearest enemy city to the caster's capital (the original's
+//     FindEnemyTarget was an explicit placeholder returning no target)
+//   - AI casting = at &gt;= 75% pool, same targeting, no popups
+//   - magic info = the spellbook popup shows the pool; mom_magic's 10-round
+//     status popup stays
+//
+// Base-verified forms used: Distance(loc,loc) (slicfunc.cpp Slic_Distance),
+// CreateUnit(player,int,loc,int) (Slic_CreateUnit, 4 args), UnitDB(),
+// GetCityByIndex/CityIsValid (mom_func), messagebox Button(ID_X){...}
+// (tut2_msg.slc), Message(g.player,'Segment'), {scalar} interpolation.
+// SLIC NAMESPACE IS FLAT: handlers MomSpell*, messageboxes MomMsg*,
+// string keys MOM_MSG_* -- grep uniq -d before adding names.
+// MomSpellPromptArmed[31], MomSpellCurDisp, MomSpellMaxDisp are declared in
+// mom_func.slc (the first include). Moved 2026-07-25: declaring them here, in the
+// LAST include, is the documented MagicMenu failure mode for segments that
+// interpolate them.
+// Cost table (pool caps are 100-300 per school, mom_magic M2):
+//   Flame Strike 50, Demon Strike 100 -- literals below, documented here.
+// MomCastAtNearestEnemy was REMOVED 2026-07-25: its only callers were the two
+// cast functions below, and both had to inline it anyway (a Button body cannot
+// reach a user function two levels deep -- see MomCastFlameStrike). Keeping an
+// uncallable helper around would just invite someone to call it again.
+// Flame Strike: any sphere; projects the caster's sphere creature at the
+// nearest enemy city. Cost 50.
+//
+// FLAT ON PURPOSE -- do not "clean this up" by calling MomSphereSummonUnit and
+// MomCastAtNearestEnemy. MEASURED 2026-07-25 (bisect, casts disabled = 25-turn
+// run survives, casts enabled = 0xC0000005 with no SLIC error dialog): a Button
+// or trigger body gets ONE level of user call, and that callee must not call
+// another user function. HandleEvent bodies are more generous -- mom_magic's
+// BeginTurn goes handler -&gt; MomSphereSummonUnit -&gt; MomPlayerIsLife every turn
+// without incident -- so the budget is per ENTRY POINT, not global. The sphere
+// lookup (mom_magic.slc:52) and the targeting scan (MomCastAtNearestEnemy above)
+// are therefore inlined here.
+void_f MomCastFlameStrike(int_t p)
+{
+    int_t i;
+    int_t j;
+    int_t best;
+    int_t d;
+    int_t found;
+    int_t summon;
+    city_t homeCity;
+    city_t tmpCity;
+    location_t homeLoc;
+    location_t bestLoc;
+    if (p &gt;= 1) {
+        if (MomMagicCur[p] &lt; 50) {
+            if (IsHumanPlayer(p)) {
+                Message(g.player, 'MomMsgNoMana');
+            }
+        } else {
+            // inlined MomSphereSummonUnit: seating is player N == civ N
+            summon = 0;
+            if (p == 1) { summon = UnitDB(UNIT_GUARDIAN_SPIRIT); }
+            if (p == 2) { summon = UnitDB(UNIT_WARBEARS); }
+            if (p == 3) { summon = UnitDB(UNIT_MAGE); }
+            if (p == 4) { summon = UnitDB(UNIT_ZOMBIES); }
+            if (p == 5) { summon = UnitDB(UNIT_HELL_HOUNDS); }
+            // inlined MomCastAtNearestEnemy(p, summon, 50, 0)
+            found = 0;
+            best = 999999;
+            if (player[0].cities &gt; 0 &amp;&amp; summon != 0) {
+                GetCityByIndex(player[0], 0, homeCity);
+                if (CityIsValid(homeCity)) {
+                    homeLoc = homeCity.location;
+                    // MEASURED 2026-07-25: assigning player[2] = i for every i in
+                    // 1..30 and then reading .cities dereferences player slots that
+                    // do not exist -- a deterministic 0xC0000005 the first time this
+                    // scan runs. This is reached from MomSpellAICast at &gt;= 75% pool,
+                    // which is why every headless run died at turn 7 with a clean
+                    // hook log and no SLIC error. IsPlayerAlive is base-verified
+                    // (present in ctp2.exe, used throughout AlexanderTheGreat) and is
+                    // a BUILTIN, so it costs nothing against the nested-call budget.
+                    for (i = 1; i &lt; 31; i = i + 1) {
+                        if (i != p &amp;&amp; IsPlayerAlive(i)) {
+                        player[2] = i;
+                        if (player[2].cities &gt; 0) {
+                            for (j = 0; j &lt; player[2].cities; j = j + 1) {
+                                GetCityByIndex(player[2], j, tmpCity);
+                                if (CityIsValid(tmpCity)) {
+                                    d = Distance(homeLoc, tmpCity.location);
+                                    if (d &lt; best) {
+                                        best = d;
+                                        bestLoc = tmpCity.location;
+                                        found = 1;
+                                    }
+                                }
+                            }
+                        }
+                        }
+                    }
+                    if (found == 1) {
+                        MomMagicCur[p] = MomMagicCur[p] - 50;
+                        CreateUnit(p, summon, bestLoc, 2);
+                        if (IsHumanPlayer(p)) {
+                            MomSpellCurDisp = MomMagicCur[p];
+                            MomSpellMaxDisp = MomMagicMax[p];
+                            Message(g.player, 'MomMsgFlameCast');
+                        }
+                    } else {
+                        if (IsHumanPlayer(p)) {
+                            Message(g.player, 'MomMsgNoTarget');
+                        }
+                    }
+                }
+            }
+        }
+    }
+}
+// Demon Strike: Chaos school only (original rule). Cost 100.
+void_f MomCastDemonStrike(int_t p)
+{
+    int_t i;
+    int_t j;
+    int_t best;
+    int_t d;
+    int_t found;
+    city_t homeCity;
+    city_t tmpCity;
+    location_t homeLoc;
+    location_t bestLoc;
+    if (p &gt;= 1) {
+        // Inlined (p == 5) rather than MomPlayerIsChaos(p): this runs from a
+        // Button body, and a nested user call on that path is the measured
+        // 0xC0000005 documented in MomSpellShowBook below.
+        if (p != 5) {
+            if (IsHumanPlayer(p)) {
+                Message(g.player, 'MomMsgNotChaos');
+            }
+        } else {
+            if (MomMagicCur[p] &lt; 100) {
+                if (IsHumanPlayer(p)) {
+                    Message(g.player, 'MomMsgNoMana');
+                }
+            } else {
+                // Flat for the same reason as MomCastFlameStrike -- see the note
+                // there. This is reached from a Button body.
+                found = 0;
+                best = 999999;
+                if (player[0].cities &gt; 0) {
+                    GetCityByIndex(player[0], 0, homeCity);
+                    if (CityIsValid(homeCity)) {
+                        homeLoc = homeCity.location;
+                        // Same dead-player-slot guard as MomCastFlameStrike above.
+                        for (i = 1; i &lt; 31; i = i + 1) {
+                            if (i != p &amp;&amp; IsPlayerAlive(i)) {
+                            player[2] = i;
+                            if (player[2].cities &gt; 0) {
+                                for (j = 0; j &lt; player[2].cities; j = j + 1) {
+                                    GetCityByIndex(player[2], j, tmpCity);
+                                    if (CityIsValid(tmpCity)) {
+                                        d = Distance(homeLoc, tmpCity.location);
+                                        if (d &lt; best) {
+                                            best = d;
+                                            bestLoc = tmpCity.location;
+                                            found = 1;
+                                        }
+                                    }
+                                }
+                            }
+                            }
+                        }
+                        if (found == 1) {
+                            MomMagicCur[p] = MomMagicCur[p] - 100;
+                            CreateUnit(p, UnitDB(UNIT_DEMON), bestLoc, 2);
+                            if (IsHumanPlayer(p)) {
+                                MomSpellCurDisp = MomMagicCur[p];
+                                MomSpellMaxDisp = MomMagicMax[p];
+                                Message(g.player, 'MomMsgDemonCast');
+                            }
+                        } else {
+                            if (IsHumanPlayer(p)) {
+                                Message(g.player, 'MomMsgNoTarget');
+                            }
+                        }
+                    }
+                }
+            }
+        }
+    }
+}
+// Show the spellbook popup for player p (pool status + cast buttons).
+void_f MomSpellShowBook(int_t p)
+{
+    if (p &gt;= 1) {
+        MomSpellCurDisp = MomMagicCur[p];
+        MomSpellMaxDisp = MomMagicMax[p];
+        // NESTED USER-FUNCTION CALLS CRASH ON THE TRIGGER PATH (measured
+        // 2026-07-25, three runs, one variable each):
+        //   trigger -&gt; inline Message                       = OK
+        //   trigger -&gt; MomSpellShowBook -&gt; Message          = OK
+        //   trigger -&gt; MomSpellShowBook -&gt; MomPlayerIsChaos = 0xC0000005
+        // One level of user call from a trigger body is fine; a SECOND level is
+        // not. No SLIC error dialog -- the process dies. An explicit `== 1`
+        // comparison does NOT help; the crash is the nested call itself, not the
+        // truthiness form. MomPlayerIsChaos is just `p == 5` (mom_func.slc:49),
+        // so inline the comparison here rather than call it. Any other helper
+        // reached from a trigger or Button body needs the same treatment.
+        if (p == 5) {
+            Message(g.player, 'MomMsgSpellbookChaos');
+        } else {
+            Message(g.player, 'MomMsgSpellbook');
+        }
+    }
+}
+// Player spellbook: offered once each time the pool crosses 60% of max
+// (re-armed when it drops back below). Chaos gets the extra Demon button.
+// (On-demand access will come from the Ritual Circle trigger improvement.)
+HandleEvent(BeginTurn) 'MomSpellMenuTick' post {
+    int_t p;
+    int_t threshold;
+    p = player[0];
+    // TEMP PROBE REMOVED 2026-07-25. It called MomSpellShowBook unconditionally
+    // every BeginTurn, so its Message stacked on mom_magic's own BeginTurn
+    // message in the same event. MEASURED: 2/2 runs crashed (game window gone,
+    // no crash.txt) with this handler enabled and 2/2 passed with it disabled;
+    // the other two entry points (MomSpellAICast, the MagicButton trigger) were
+    // cleared by the same bisect. This is the queue-flood class already
+    // documented at scenario.slc:33 -- an unlatched Message in BeginTurn floods
+    // the queue -&gt; 0xC0000005. The threshold logic below is correctly latched
+    // (MomSpellPromptArmed re-arms only after the pool drops back under 60%),
+    // which is why it is safe to keep.
+    if (p &gt;= 1 &amp;&amp; IsHumanPlayer(p) &amp;&amp; MomMagicMax[p] &gt; 0) {
+        threshold = (MomMagicMax[p] * 3) / 5;
+        if (MomMagicCur[p] &lt; threshold) {
+            MomSpellPromptArmed[p] = 1;
+        }
+        if (MomSpellPromptArmed[p] == 1 &amp;&amp; MomMagicCur[p] &gt;= threshold) {
+            MomSpellPromptArmed[p] = 0;
+            // AUTO-POPUP REMOVED 2026-07-25. Latched or not, this put a MODAL on
+            // screen at BeginTurn on top of mom_magic's own status box. Unread SLIC
+            // messages QUEUE, they do not replace each other, so from the first
+            // crossing onward every turn starts with two stacked modals; the
+            // end-turn click lands on a box instead of the button and the
+            // playthrough stalls (measured: TURN_DID_NOT_ADVANCE_AT_6). Blind-
+            // dismissing them is worse -- the fixed close coordinate lands on a
+            // CAST button on this box, firing a spell nobody asked for. The
+            // spellbook is on-demand only now, via the 'MomOpenSpellbook' trigger
+            // below (verified headless: MagicButton -&gt; SPELLBOOK alertbox).
+            // The latch bookkeeping above is kept so a future opt-in re-arm still
+            // has correct state.
+        }
+    }
+}
+// On-demand access: a native SLIC UI-component trigger, NOT a keypress.
+// REVERTED (2026-07-18): the keyboard path (SetActionKey/RunKeyboardTrigger
+// ActionKey&lt;N&gt; dispatch, an engine C++ patch) worked mechanically but froze
+// the game on first real test, AND 'm' collides with the base game's own
+// keymap.txt binding (m -&gt; MOVE_ORDER) -- a real player loses unit-move
+// orders for as long as this scenario is loaded. No engine patch needed for
+// this at all: `trigger 'X' on "LDL.Control.Path" when(cond) {...}` is a
+// standard, ALREADY-WORKING SLIC mechanism (fires via
+// HandleGameSpecificLeftClick -&gt; SlicEngine::RunUITriggers for any
+// LDL-defined clickable control; 15+ proven examples in base
+// ctp2_data/default/gamedata/tut2_main.slc, e.g. 'TSPScience' on
+// "ControlPanelWindow.ControlPanel.ShortcutPad.ScienceButton"). Event-driven
+// (fires once per real click) and repeatable (omitting DisableTrigger(), as
+// the base one-shot tutorial triggers deliberately call it and we don't).
+trigger 'MomOpenSpellbook' on "ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton" when (1) {
+    MomSpellShowBook(g.player);
+}
+// AI spellcasting (the momjr original gated at 75% of max but its targeting
+// was a placeholder that never found a target): at &gt;= 75% pool the AI casts
+// for real -- Chaos AIs prefer Demon Strike, everyone else Flame Strike.
+HandleEvent(BeginTurn) 'MomSpellAICast' post {
+    int_t p;
+    p = player[0];
+    if (p &gt;= 1 &amp;&amp; IsHumanPlayer(p) == 0 &amp;&amp; MomMagicMax[p] &gt; 0) {
+        if (MomMagicCur[p] * 4 &gt;= MomMagicMax[p] * 3) {
+            // Inlined chaos test -- see MomSpellShowBook for the nested-call crash.
+            if (p == 5 &amp;&amp; MomMagicCur[p] &gt;= 100) {
+                MomCastDemonStrike(p);
+            } else {
+                MomCastFlameStrike(p);
+            }
+        }
+    }
+}
+// ---------------------------------------------------------------------------
+// Messagebox segments (see lessons_learned 2026-07-17: Message() requires a
+// DEFINED segment; names must not collide with handlers or string keys).
+// ---------------------------------------------------------------------------
+alertbox 'MomMsgSpellbook' {
+    Show();
+    Text(ID_MOM_MSG_SPELLBOOK);
+    Button(ID_BUTTON_RESEARCH) {
+        MomCastFlameStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+}
+alertbox 'MomMsgSpellbookChaos' {
+    Show();
+    Text(ID_MOM_MSG_SPELLBOOK);
+    Button(ID_BUTTON_GOAL) {
+        MomCastDemonStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_RESEARCH) {
+        MomCastFlameStrike(g.player);
+        Kill();
+    }
+    Button(ID_BUTTON_CLOSE) {
+        Kill();
+    }
+}
+alertbox 'MomMsgDemonCast' {
+    Show();
+    Text(ID_MOM_MSG_DEMON_CAST);
+}
+alertbox 'MomMsgFlameCast' {
+    Show();
+    Text(ID_MOM_MSG_FLAME_CAST);
+}
+alertbox 'MomMsgNoTarget' {
+    Show();
+    Text(ID_MOM_MSG_NO_TARGET);
+}
+alertbox 'MomMsgNoMana' {
+    Show();
+    Text(ID_MOM_MSG_NO_MANA);
+}
+alertbox 'MomMsgNotChaos' {
+    Show();
+    Text(ID_MOM_MSG_NOT_CHAOS);
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>tutorial.slc</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>retires stock tut2_main.slc tutorial triggers</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>758</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>//=============================================================================
+// tutorial.slc -- Master of Magic override: stock tutorial SLIC RETIRED
+//=============================================================================
+// The base ctp2_data/default/gamedata/tutorial.slc does
+//   #include "tut2_main.slc"
+// which activates Activision's stock tutorial triggers (TStartGame etc.) --
+// unwanted inside a total-conversion fantasy scenario. This scenario-level
+// override shadows the base file and includes nothing.
+//
+// tut2_main.slc is intentionally left on disk untouched; it simply no longer
+// loads. Remove this file to restore the stock tutorial behaviour.
+//=============================================================================</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>signature</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>MomPlayerIsLife</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_1)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>faction predicate p==1 (Life)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>MomPlayerIsNature</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_2)</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>faction predicate p==2 (Nature)</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>MomPlayerIsSorcery</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_3)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>faction predicate p==3 (Sorcery)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>MomPlayerIsDeath</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_4)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>faction predicate p==4 (Death)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MomPlayerIsChaos</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_5)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>faction predicate p==5 (Chaos)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>MomCountLifeBlessings</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_6)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>weighted count of Life buildings (TEMPLE/CITY_WALLS/WIZARDS_FORTRESS)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>MomCountNatureFoci</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_7)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>weighted count of Nature buildings (GRANARY/PRIMAL_SOURCE/FANTASTIC_STABLE)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>MomCountSorceryFoci</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t p_8)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>weighted count of Sorcery buildings (LIBRARY/BEACON_OF_WISDOM)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>MomGrantLifeBuilding</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p_9)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>grant the Life-sphere themed building in the player's first city</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>MomGrantNatureBuilding</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p_10)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>grant the Nature-sphere themed building in the player's first city</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>MomGrantSorceryBuilding</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p_11)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>grant the Sorcery-sphere themed building in the player's first city</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>MomGrantDeathBuilding</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p_12)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>grant the Death-sphere themed building in the player's first city</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>mom_func.slc</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>MomSpawnSphereUnit</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p_13, int_t unitType)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>CreateUnit in first city (integer player index)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>mom_turns.slc</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>MomSphereTurnBlessings</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>per-turn sphere gold income by faction</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>mom_city_effects.slc</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>MomSphereAdvanceBlessings</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>sphere magic-advance milestone: grant blessing building + spawn sphere unit (Chaos = random gold)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>mom_city_effects.slc</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>MomSphereCityEffects</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(CreateBuilding) post</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+30 burst gold on themed building completion</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>MomSphereBlessingMessages</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>per-sphere blessing popup on the magic advance (human-only; base Message plumbing)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonOrderTick</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>spawn the creature ordered last turn, resolved from the CASTER'S OWN sphere; debits 75 mana</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgSlicAlive</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>segment: SLIC liveness confirmation text</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>MomBlessLife</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>segment: Life sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>MomBlessNature</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>segment: Nature sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>MomBlessSorcery</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>segment: Sorcery sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>MomBlessDeath</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>segment: Death sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>MomBlessChaos</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>segment: Chaos sphere blessing popup</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonGuard</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>segment: Life summon result (Guardian Spirit) -- names the creature, so one frame settles which branch ran</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonBear</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>segment: Nature summon result (War Bear)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonMage</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>segment: Sorcery summon result (Mage)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonZombie</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>segment: Death summon result (Zombies)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonHound</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>segment: Chaos summon result (Hell Hound)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>MomSummonNoMana</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>segment: insufficient-mana answer for the Summon arm; messagebox NOT alertbox, so no modal stacks on the Kill() path</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>MomMagicPower</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>messagebox</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>segment: mana pool / income readout body</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>mom_msg.slc</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>MagicMenu</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>INTERACTIVE: MAGIC STATUS alertbox; Summon arm (75 mana) writes an order global that survives the turn boundary</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>mom_magic.slc</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>MomRecalcMagicPerTurn</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>int_f(int_t mp_1)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>recompute a player's mana income from cities + owned mana nodes (base 10/turn)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>mom_magic.slc</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>MomMagicPoolTick</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>per-turn mana accrual into MomMagicCur, capped at the 100 pool ceiling</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>mom_magic.slc</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>MomMagicSchoolGrant</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(GrantAdvance) post</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>apply per-school mana multipliers when a magic advance is granted</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>MomCastFlameStrike</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Chaos spell: damage the nearest enemy unit; targeting scan inlined to stay inside the Class 1 call budget</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>MomCastDemonStrike</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Death spell: damage the nearest enemy unit; targeting scan inlined for the same reason</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>MomSpellShowBook</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>void_f(int_t p)</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>open the spellbook popup, choosing the per-sphere variant at call time</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>MomSpellMenuTick</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>per-turn tick that resolves a queued spellbook selection</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>MomOpenSpellbook</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>on ControlPanelWindow.ControlPanel.ShortcutPad.MagicButton</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>UI trigger bound to the control-panel MagicButton</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>handler</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>MomSpellAICast</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>HandleEvent(BeginTurn) post</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>let AI players cast their sphere's spell when mana allows</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgSpellbook</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>segment: generic spellbook menu</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgSpellbookChaos</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>segment: Chaos-specific spellbook menu</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgDemonCast</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>segment: Demon Strike cast confirmation</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgFlameCast</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>segment: Flame Strike cast confirmation</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgNoTarget</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>segment: no enemy unit in range</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgNoMana</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>segment: insufficient mana for a spell (alertbox; distinct from mom_msg's summon variant)</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>mom_spells.slc</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>MomMsgNotChaos</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>alertbox</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>segment: caster's sphere does not grant this spell</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G49"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -32461,7 +37655,6 @@
           <t>286</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32474,13 +37667,11 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32503,7 +37694,6 @@
           <t>198</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32516,13 +37706,11 @@
           <t>333</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E6"/>
